--- a/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
+++ b/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B8F23A-0947-4049-B78A-DA9B0CA58E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CD6FC3-165A-4F8C-9A3F-053E22B4C311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <r>
       <rPr>
@@ -987,6 +987,135 @@
   pctfree 10
   initrans 2
   maxtrans 255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 1M
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablespace USERS
+  pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2016,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776567A7-D8E9-40E1-82FD-FF3EE741B0B4}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
@@ -2155,25 +2284,25 @@
     </row>
     <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="45" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D27" s="46"/>
       <c r="E27" s="47"/>
       <c r="G27" s="45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H27" s="46"/>
       <c r="I27" s="47"/>
       <c r="K27" s="45" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L27" s="46"/>
       <c r="M27" s="47"/>
-      <c r="O27" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="23"/>
+      <c r="O27" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="47"/>
     </row>
     <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="48"/>
@@ -2185,9 +2314,9 @@
       <c r="K28" s="48"/>
       <c r="L28" s="49"/>
       <c r="M28" s="50"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="26"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="50"/>
     </row>
     <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="48"/>
@@ -2199,9 +2328,9 @@
       <c r="K29" s="48"/>
       <c r="L29" s="49"/>
       <c r="M29" s="50"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="26"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="50"/>
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="48"/>
@@ -2213,9 +2342,9 @@
       <c r="K30" s="48"/>
       <c r="L30" s="49"/>
       <c r="M30" s="50"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="26"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="50"/>
     </row>
     <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="48"/>
@@ -2227,9 +2356,9 @@
       <c r="K31" s="48"/>
       <c r="L31" s="49"/>
       <c r="M31" s="50"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="50"/>
     </row>
     <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="51"/>
@@ -2241,16 +2370,274 @@
       <c r="K32" s="51"/>
       <c r="L32" s="52"/>
       <c r="M32" s="53"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="53"/>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C34" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="46"/>
+      <c r="E34" s="47"/>
+      <c r="G34" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C35" s="48"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="50"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="50"/>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C36" s="48"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="50"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="50"/>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C37" s="48"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="50"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="50"/>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C38" s="48"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="50"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="50"/>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C39" s="51"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="53"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="53"/>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C43" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="22"/>
+      <c r="E43" s="23"/>
+      <c r="G43" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="23"/>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="26"/>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26"/>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C47" s="24"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="26"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26"/>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C48" s="27"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="29"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="29"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C50" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="46"/>
+      <c r="E50" s="47"/>
+      <c r="G50" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="46"/>
+      <c r="I50" s="47"/>
+      <c r="K50" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="L50" s="46"/>
+      <c r="M50" s="47"/>
+      <c r="O50" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="47"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C51" s="48"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="50"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="50"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="49"/>
+      <c r="M51" s="50"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="49"/>
+      <c r="Q51" s="50"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C52" s="48"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="50"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="50"/>
+      <c r="K52" s="48"/>
+      <c r="L52" s="49"/>
+      <c r="M52" s="50"/>
+      <c r="O52" s="48"/>
+      <c r="P52" s="49"/>
+      <c r="Q52" s="50"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C53" s="48"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="50"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="50"/>
+      <c r="K53" s="48"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="50"/>
+      <c r="O53" s="48"/>
+      <c r="P53" s="49"/>
+      <c r="Q53" s="50"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C54" s="48"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="50"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="50"/>
+      <c r="K54" s="48"/>
+      <c r="L54" s="49"/>
+      <c r="M54" s="50"/>
+      <c r="O54" s="48"/>
+      <c r="P54" s="49"/>
+      <c r="Q54" s="50"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C55" s="51"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="53"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="53"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="53"/>
+      <c r="O55" s="51"/>
+      <c r="P55" s="52"/>
+      <c r="Q55" s="53"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C57" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" s="46"/>
+      <c r="E57" s="47"/>
+      <c r="G57" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" s="46"/>
+      <c r="I57" s="47"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C58" s="48"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="50"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="50"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C59" s="48"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="50"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="50"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C60" s="48"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="50"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="50"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C61" s="48"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="50"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="50"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C62" s="51"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="53"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="15">
+    <mergeCell ref="C34:E39"/>
+    <mergeCell ref="G34:I39"/>
+    <mergeCell ref="K50:M55"/>
+    <mergeCell ref="O50:Q55"/>
+    <mergeCell ref="C57:E62"/>
+    <mergeCell ref="G57:I62"/>
     <mergeCell ref="C4:H7"/>
     <mergeCell ref="C27:E32"/>
+    <mergeCell ref="G50:I55"/>
+    <mergeCell ref="C50:E55"/>
+    <mergeCell ref="C43:E48"/>
+    <mergeCell ref="G43:I48"/>
+    <mergeCell ref="G27:I32"/>
     <mergeCell ref="K27:M32"/>
-    <mergeCell ref="G27:I32"/>
     <mergeCell ref="O27:Q32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
+++ b/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CD6FC3-165A-4F8C-9A3F-053E22B4C311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7452DE-5C93-4631-9215-80F241EEE1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,14 +11,16 @@
     <sheet name="概述" sheetId="1" r:id="rId1"/>
     <sheet name="安装" sheetId="2" r:id="rId2"/>
     <sheet name="迁移" sheetId="11" r:id="rId3"/>
-    <sheet name="基础" sheetId="10" r:id="rId4"/>
-    <sheet name="语法" sheetId="5" r:id="rId5"/>
-    <sheet name="知识点" sheetId="3" r:id="rId6"/>
-    <sheet name="示例" sheetId="6" r:id="rId7"/>
-    <sheet name="重点" sheetId="9" r:id="rId8"/>
-    <sheet name="总结" sheetId="4" r:id="rId9"/>
-    <sheet name="问题" sheetId="8" r:id="rId10"/>
-    <sheet name="参考" sheetId="7" r:id="rId11"/>
+    <sheet name="oracle" sheetId="13" r:id="rId4"/>
+    <sheet name="基础" sheetId="10" r:id="rId5"/>
+    <sheet name="语法" sheetId="5" r:id="rId6"/>
+    <sheet name="知识点" sheetId="3" r:id="rId7"/>
+    <sheet name="示例" sheetId="6" r:id="rId8"/>
+    <sheet name="重点" sheetId="9" r:id="rId9"/>
+    <sheet name="包" sheetId="12" r:id="rId10"/>
+    <sheet name="总结" sheetId="4" r:id="rId11"/>
+    <sheet name="问题" sheetId="8" r:id="rId12"/>
+    <sheet name="参考" sheetId="7" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="207">
   <si>
     <r>
       <rPr>
@@ -1118,12 +1120,1071 @@
   )</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>创建主键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE UNIQUE INDEX UQ01_mbom_t_route_base ON fawbom.mbom_t_route_base(EMAIL);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALTER TABLE fawbom.mbom_t_route_base ADD CONSTRAINT PK_mbom_t_route_base PRIMARY KEY (route_id);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE FUNCTION public.gen_random_uuid()
+RETURNS character varying
+LANGUAGE sql
+NOT FENCED NOT SHIPPABLE
+AS $function$
+    SELECT replace(md5(random()::text || clock_timestamp()::text)::text,'-','');
+$function$;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenGauss中的语法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gen_random_uuid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE FUNCTION public.gen_random_uuid()
+ RETURNS string
+AS 
+BEGIN
+    RETURN sys_guid();
+END
+;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金仓数据库执行报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金仓数据库支持：sys_guid()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建GUID函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KingbaseES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在KSQL Developer中创建包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    /*日志输出*/
+  Procedure put_line(i_remark varchar);
+END</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+  /*日志输出*/
+  Procedure put_line(i_remark varchar)
+  is
+  begin
+          raise notice '%',i_remark;
+  end;    
+BEGIN
+    NULL;
+END</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEGIN 
+	"public"."dbms_output"."put_line"('22');
+END</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>或</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECLARE n_cnt number(6):=66; 
+BEGIN 
+	public.dbms_output.put_line(n_cnt);
+END</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHOW database_mode;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示兼容模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 1M
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 1M
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 16K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 1
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using index
+  tablespace USERS
+  pctfree 10
+  initrans 2
+  maxtrans 255
+  storage
+  (
+    initial 64K
+    next 8K
+    minextents 1
+    maxextents unlimited
+  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：因为部分替换内容存在包含关系，所以替换得从没有被其他字符包括的开始替换！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle兼容模式下的金仓数据与Oracle数据库中用户、模式的差异</t>
+  </si>
+  <si>
+    <r>
+      <t>KingbaseES 在 Oracle 兼容模式下，虽然提供了高度兼容的语法和功能，但在核心的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>用户（User）与模式（Schema）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 架构上，两者存在根本性差异。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>核心区别在于：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>在Oracle中，用户和模式是“一体”的；而在KingbaseES中，它们是“分离”的。</t>
+    </r>
+  </si>
+  <si>
+    <t>核心差异：用户与模式的关系</t>
+  </si>
+  <si>
+    <t>Oracle：用户即模式，一一对应</t>
+  </si>
+  <si>
+    <t>在Oracle中，创建一个用户时会自动创建一个与之同名的模式（Schema）。这个模式是该用户的“私有领地”，默认情况下，用户只能访问自己模式下的对象，两者是紧密绑定、不可分割的。</t>
+  </si>
+  <si>
+    <t>KingbaseES：用户与模式相互独立</t>
+  </si>
+  <si>
+    <t>这是两者最本质的区别。KingbaseES将用户和模式视为两个独立的概念。</t>
+  </si>
+  <si>
+    <r>
+      <t>用户（User）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：是一个用于登录数据库的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>账户实体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>模式（Schema）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：是一个用于组织和隔离数据库对象的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>逻辑命名空间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>这种设计带来了更高的灵活性：</t>
+  </si>
+  <si>
+    <r>
+      <t>多对多关系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：一个用户可以拥有（或访问）多个模式；反过来，一个模式也可以被多个用户共享。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>逻辑分组</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：你可以将不同应用或功能模块的表、视图、函数等放在不同的模式下进行管理，实现更清晰的逻辑隔离。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>避免对象丢失风险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：在Oracle中，如果删除了一个用户，其同名模式下的所有对象也会被级联删除。而在KingbaseES中，由于用户与模式解绑，你可以在不删除模式的情况下删除或停用一个用户，从而保护数据资产。</t>
+    </r>
+  </si>
+  <si>
+    <t>核心差异：默认管理员与预置模式</t>
+  </si>
+  <si>
+    <t>• Oracle：默认的管理员账户是 SYS 和 SYSTEM。</t>
+  </si>
+  <si>
+    <t>• KingbaseES：出于安全考虑，采用了“三权分立”的设计，初始化后默认创建三个管理员账户-</t>
+  </si>
+  <si>
+    <t>◦ system：数据库管理员</t>
+  </si>
+  <si>
+    <t>◦ sso：安全管理员</t>
+  </si>
+  <si>
+    <t>◦ sao：审计管理员</t>
+  </si>
+  <si>
+    <t>此外，KingbaseES在创建数据库时会默认生成 SYS_CATALOG（存放系统表）和 PUBLIC（通常作为默认模式）两个模式-</t>
+  </si>
+  <si>
+    <t>权限与角色管理</t>
+  </si>
+  <si>
+    <t>• 语法高度兼容：在用户和角色的创建、授权语法上，KingbaseES与Oracle高度兼容-</t>
+  </si>
+  <si>
+    <t>◦ 创建用户：CREATE USER username IDENTIFIED BY password;</t>
+  </si>
+  <si>
+    <t>◦ 授权：GRANT SELECT ON table TO user;</t>
+  </si>
+  <si>
+    <t>• “用户”与“角色”：KingbaseES中，用户（USER）和角色（ROLE）本质上相同，核心区别在于用户拥有 LOGIN（登录）权限，而角色没有-</t>
+  </si>
+  <si>
+    <t>• 权限模型：都采用“用户 → 角色 → 权限”的三层模型-</t>
+  </si>
+  <si>
+    <t>◦ 系统权限：大部分Oracle的系统权限在KingbaseES中都有对应实现（如 CREATE SESSION 对应 LOGIN）-</t>
+  </si>
+  <si>
+    <t>◦ 细粒度控制：KingbaseES支持更细粒度的权限控制，例如可以更灵活地控制 WITH GRANT OPTION 的传播-</t>
+  </si>
+  <si>
+    <t>安全策略</t>
+  </si>
+  <si>
+    <t>两者都提供强大的安全功能，但实现方式略有不同。</t>
+  </si>
+  <si>
+    <t>安全功能</t>
+  </si>
+  <si>
+    <t>Oracle</t>
+  </si>
+  <si>
+    <t>行级安全 (RLS)</t>
+  </si>
+  <si>
+    <r>
+      <t>通过 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DBMS_RLS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 包实现策略函数。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>支持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SECURITY POLICY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 语法实现。</t>
+    </r>
+  </si>
+  <si>
+    <t>密码策略</t>
+  </si>
+  <si>
+    <r>
+      <t>通过 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PROFILE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 配置文件管理。</t>
+    </r>
+  </si>
+  <si>
+    <t>内置了密码复杂度校验、有效期和登录失败锁定等策略。</t>
+  </si>
+  <si>
+    <t>强制访问控制 (MAC)</t>
+  </si>
+  <si>
+    <r>
+      <t>需要额外购买 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Label Security</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 选项。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>内建支持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>，无需额外组件</t>
+    </r>
+  </si>
+  <si>
+    <t>迁移时的核心注意事项</t>
+  </si>
+  <si>
+    <t>理解上述差异后，在迁移时需要特别注意以下几点：</t>
+  </si>
+  <si>
+    <r>
+      <t>1. 用户与模式的对应关系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：Oracle迁移脚本中，用户和模式是等同的。在KingbaseES中，你需要显式地管理这种对应关系。例如，可以为每个迁移来的Oracle用户创建一个同名的模式，并将其设置为该用户的默认模式。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 对象属主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：在KingbaseES中，每个对象（如表、视图）都有一个“属主”（Owner），通常是指创建它的用户。规划迁移时，需要明确每个对象的属主是谁。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. 跨模式访问</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：由于用户和模式是分离的，用户要访问自己模式之外的对象，必须被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>显式地授予</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>访问权限。迁移后，需要检查和重建这些跨模式的权限。</t>
+    </r>
+  </si>
+  <si>
+    <t>总而言之，虽然KingbaseES的Oracle兼容模式在语法层面非常接近，但其底层的用户和模式架构更为灵活。理解并利用好这种“分离”的特性，是成功从Oracle迁移并充分发挥KingbaseES优势的关键。</t>
+  </si>
+  <si>
+    <r>
+      <t>4. 公共同义词（Public Synonym）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：Oracle中常用的公共同义词在KingbaseES中可能不直接支持，可能需要通过创建视图或调整应用连接方式来替代。</t>
+    </r>
+  </si>
+  <si>
+    <t>alter table FAWBOM.ebom_t_modelprop
+  add constraint PK_ebom_t_modelprop primary key (spec_id);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包总体说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> --todo-huangguohui-20260715 待源包好后重新启用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包中函数说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包中存储过程说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+   * 包名称：【定义】
+   * 包简述：   
+   * 创建人：  
+   * 创建日期：20180623
+   * 修订历史：
+   *   20180623 新增 
+   *   20260715 将Oracle版本转换为KingbaseES适用版本 huangguohui
+   */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+  *对象名称：【】函数
+  *对象描述：
+  *重点说明：
+  *业务规则：
+  *修改历史：
+  *   20180623 新增 
+  *   20260715 转换为KingbaseES版本 huangguohui   
+  */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+  *对象名称：【】存储过程
+  *对象描述：
+  *重点说明：
+  *业务规则：
+  *修改历史：
+  *   20180623 新增 
+  *   20260715 转换为KingbaseES版本 huangguohui   
+  */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用KingbaseES数据库的官方免费连接工具来创建，步骤：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、连接数据库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、打开对应模式下的【程序包】，右击选择【新建 程序包】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法1： 可视化录入内容，见右图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法2： 直接编辑内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、录入包内容，有两种方式：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、输入包名，以dbms_output为例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别录入包头、包体，然后点击确定即可。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>录入包名后，先点确定。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右击该包，然后【生成SQL】&gt; 【DDL】&gt;【打开编辑器】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接在里边修改内容，然后点击【执行SQL脚本】即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑器模式内容：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE PACKAGE "fawbom"."dbms_output" AUTHID CURRENT_USER AS      /*日志输出*/
+  Procedure put_line(i_remark varchar);
+END;
+CREATE OR REPLACE PACKAGE BODY "fawbom"."dbms_output" AS    
+  /*日志输出*/
+  Procedure put_line(i_remark varchar)
+  is
+  begin
+          raise notice '%',i_remark;
+  end;    
+BEGIN
+    NULL;
+END
+;;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kingbase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE TYPE "EBOM_STACK"                                          As Object
+(
+--字符串堆栈
+--http://docs.oracle.com/cd/B10501_01/appdev.920/a96624/10_objs.htm
+  max_size Integer,
+  top      Integer,
+  position EBOM_CharArray,
+  Member Procedure initialize,
+  Member Function Full Return Boolean,
+  Member Function empty Return Boolean,
+  Member Function topvalue Return Varchar2,
+  Member Procedure push(var_i In Varchar2),
+  Member Procedure pop(var_o Out Varchar2),
+  Constructor Function EBOM_Stack Return Self As Result
+)
+/
+CREATE OR REPLACE TYPE BODY "EBOM_STACK" As
+  Constructor Function EBOM_Stack Return Self As Result Is
+  Begin
+    Return;
+  End;
+  Member Procedure initialize Is
+  Begin
+    top := 0;
+    position := EBOM_CharArray(Null);
+    max_size := position.LIMIT;
+    position.EXTEND(1024);
+  End initialize;
+  Member Function Full Return Boolean Is
+  Begin
+    Return(top = max_size);
+  End Full;
+  Member Function empty Return Boolean Is
+  Begin
+    Return(top = 0);
+  End empty;
+  Member Function topvalue Return Varchar2 Is
+  Begin
+    Return(position(top));
+  End topvalue;
+  Member Procedure push(var_i In Varchar2) Is
+  Begin
+    If Not Full Then
+      top := top + 1;
+      position(top) := var_i;
+    Else
+      RAISE_APPLICATION_ERROR(-20101, 'stack overflow');
+    End If;
+  End push;
+  Member Procedure pop(var_o Out Varchar2) Is
+  Begin
+    If Not empty Then
+      var_o := position(top);
+      position(top) := Null;
+      top := top - 1;
+    Else
+      RAISE_APPLICATION_ERROR(-20102, 'stack underflow');
+    End If;
+  End pop;
+End;
+/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATE OR REPLACE TYPE "EBOM_CHARARRAY"                                          FORCE                                      AS VARRAY(2000) OF VARCHAR2(2048);
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBOM_CHARARRAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kingbase测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Popped:B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATE OR REPLACE TYPE EBOM_CharArray AS VARRAY(2000) OF VARCHAR2(4000);
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE TYPE EBOM_STACK AS OBJECT
+(
+  max_size INTEGER,
+  top      INTEGER,
+  position EBOM_CharArray,
+  MEMBER PROCEDURE initialize,
+  MEMBER FUNCTION Full RETURN BOOLEAN,
+  MEMBER FUNCTION empty RETURN BOOLEAN,
+  MEMBER FUNCTION topvalue RETURN VARCHAR2,
+  MEMBER PROCEDURE push(var_i IN VARCHAR2),
+  MEMBER PROCEDURE pop(var_o OUT VARCHAR2),
+  CONSTRUCTOR FUNCTION EBOM_Stack RETURN SELF AS RESULT
+);
+/
+-- 3. 类型体（关键修正：构造函数中 RETURN 不带表达式）
+CREATE OR REPLACE TYPE BODY EBOM_STACK AS
+  -- ★ 构造函数：初始化所有属性，并 RETURN;（不带表达式）
+  CONSTRUCTOR FUNCTION EBOM_Stack RETURN SELF AS RESULT IS
+  BEGIN
+    SELF.top := 0;
+    SELF.position := EBOM_CharArray();      -- 空数组
+    SELF.max_size := SELF.position.LIMIT;   -- 返回 1024
+    SELF.position.EXTEND(2000);             -- 扩展至 1024 个元素
+    RETURN;                                 -- 不允许带表达式，仅 RETURN;
+  END;
+  -- 其余方法（已修正函数调用加括号）
+  MEMBER PROCEDURE initialize IS
+  BEGIN
+    top := 0;
+    position := EBOM_CharArray();
+    max_size := position.LIMIT;
+    position.EXTEND(2000);
+  END initialize;
+  MEMBER FUNCTION Full RETURN BOOLEAN IS
+  BEGIN
+    RETURN(top = max_size);
+  END Full;
+  MEMBER FUNCTION empty RETURN BOOLEAN IS
+  BEGIN
+    RETURN(top = 0);
+  END empty;
+  MEMBER FUNCTION topvalue RETURN VARCHAR2 IS
+  BEGIN
+    RETURN(position(top));
+  END topvalue;
+  MEMBER PROCEDURE push(var_i IN VARCHAR2) IS
+  BEGIN
+    IF NOT Full() THEN
+      top := top + 1;
+      position(top) := var_i;
+    ELSE
+      RAISE EXCEPTION 'stack overflow';
+    END IF;
+  END push;
+  MEMBER PROCEDURE pop(var_o OUT VARCHAR2) IS
+  BEGIN
+    IF NOT empty() THEN
+      var_o := position(top);
+      position(top) := NULL;
+      top := top - 1;
+    ELSE
+      RAISE EXCEPTION 'stack underflow';
+    END IF;
+  END pop;
+END;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -- 2. 对象类型声明
+CREATE OR REPLACE TYPE F119 AS OBJECT
+(
+  max_size       INTEGER,
+  first_position INTEGER,
+  last_position  INTEGER,
+  top            INTEGER,
+  position       EBOM_CharArray,
+  MEMBER PROCEDURE initialize,
+  MEMBER FUNCTION full RETURN BOOLEAN,
+  MEMBER FUNCTION empty RETURN BOOLEAN,
+  MEMBER PROCEDURE EnQueue(var_i IN VARCHAR2),
+  MEMBER PROCEDURE DeQueue(var_o OUT VARCHAR2),
+  CONSTRUCTOR FUNCTION EBOM_Queue RETURN SELF AS RESULT
+);
+/
+-- 3. 类型体（关键修改处已标注）
+CREATE OR REPLACE TYPE BODY EBOM_QUEUE AS
+  -- ★ 构造函数：初始化队列状态，并仅 RETURN;
+  CONSTRUCTOR FUNCTION EBOM_Queue RETURN SELF AS RESULT IS
+  BEGIN
+    SELF.top := 0;
+    SELF.position := EBOM_CharArray();      -- 空数组
+    SELF.max_size := SELF.position.LIMIT;   -- 1024
+    SELF.position.EXTEND(2000);             -- 分配元素
+    SELF.first_position := 1;
+    SELF.last_position  := 0;
+    RETURN;  -- 不带表达式
+  END;
+  -- 初始化方法（重置队列）
+  MEMBER PROCEDURE initialize IS
+  BEGIN
+    top := 0;
+    position := EBOM_CharArray();
+    max_size := position.LIMIT;
+    first_position := 1;
+    last_position := 0;
+    position.EXTEND(2000);
+  END initialize;
+  MEMBER FUNCTION full RETURN BOOLEAN IS
+  BEGIN
+    RETURN(top = max_size);
+  END full;
+  MEMBER FUNCTION empty RETURN BOOLEAN IS
+  BEGIN
+    RETURN(top = 0);
+  END empty;
+  MEMBER PROCEDURE EnQueue(var_i IN VARCHAR2) IS
+  BEGIN
+    IF NOT full() THEN  -- 必须加括号
+      last_position := last_position + 1;
+      IF last_position &gt; max_size THEN
+        last_position := 1;  -- 循环索引重置为 1（数组下标从1开始）
+      END IF;
+      position(last_position) := var_i;
+      top := top + 1;
+    ELSE
+      RAISE EXCEPTION 'Queue overflow';
+    END IF;
+  END EnQueue;
+  MEMBER PROCEDURE DeQueue(var_o OUT VARCHAR2) IS
+  BEGIN
+    IF NOT empty() THEN  -- 必须加括号
+      var_o := position(first_position);
+      first_position := first_position + 1;
+      IF first_position &gt; max_size THEN
+        first_position := 1;
+      END IF;
+      top := top - 1;
+    ELSE
+      RAISE EXCEPTION 'Queue underflow';
+    END IF;
+  END DeQueue;
+END;
+/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBOM_QUEUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*测试queue*/
+DECLARE
+  q EBOM_QUEUE;
+  v VARCHAR2(100);
+BEGIN
+  q := EBOM_QUEUE();          -- 构造函数自动初始化
+  q.EnQueue('First');
+  q.EnQueue('Second');
+  q.DeQueue(v);
+  raise notice 'DeQueued: %',v;   -- 输出 "DeQueued: First"
+  q.DeQueue(v);
+  raise notice'DeQueued: %',v;   -- 输出 "DeQueued: Second"
+END;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeQueued: First</t>
+  </si>
+  <si>
+    <t>DeQueued: Second</t>
+  </si>
+  <si>
+    <t>EBOM_STACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*测试stack*/
+DECLARE
+  s EBOM_STACK;
+  v VARCHAR2(100);
+BEGIN
+  s := EBOM_STACK();          -- 构造函数自动初始化
+  s.push('A');
+  s.push('B');
+  s.pop(v);
+  raise notice 'Popped:%',v;   -- 输出 "Popped: B"
+END;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle原栈和队列自定义数据类型转换：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1292,19 +2353,6 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -1329,8 +2377,89 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1340,6 +2469,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1451,7 +2586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1495,37 +2630,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1533,6 +2638,132 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1557,41 +2788,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1635,6 +2842,81 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1BE9A50-F158-4739-96A0-A968DD478494}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8705850" y="161925"/>
+          <a:ext cx="6896100" cy="6915150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1908,9 +3190,9 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1978,7 +3260,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="41" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="16" t="s">
@@ -1989,7 +3271,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="19"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="18" t="s">
         <v>24</v>
       </c>
@@ -1998,7 +3280,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="41" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="16" t="s">
@@ -2009,7 +3291,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="19"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="18" t="s">
         <v>50</v>
       </c>
@@ -2018,7 +3300,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="41" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -2029,7 +3311,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="19"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="18" t="s">
         <v>32</v>
       </c>
@@ -2038,7 +3320,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="41" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -2049,7 +3331,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B31" s="19"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="17" t="s">
         <v>37</v>
       </c>
@@ -2058,7 +3340,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="41" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="16" t="s">
@@ -2069,7 +3351,7 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B33" s="19"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="17" t="s">
         <v>42</v>
       </c>
@@ -2078,7 +3360,7 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="41" t="s">
         <v>45</v>
       </c>
       <c r="C34" s="16" t="s">
@@ -2089,7 +3371,7 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B35" s="19"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="18" t="s">
         <v>47</v>
       </c>
@@ -2113,6 +3395,354 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6BF04C-161C-4666-8967-A5292F682366}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="80" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="44"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="45"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="47"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" s="45"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="47"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="48"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="50"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="80" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="44"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="H11" s="45"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="47"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="H12" s="45"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="47"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="47"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="45"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="47"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="47"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="47"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="45"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="47"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="45"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="47"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="50"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="45"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="47"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="45"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="47"/>
+      <c r="H21" s="80" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="47"/>
+      <c r="H22" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="45"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="47"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="47"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="47"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="47"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="47"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="50"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47"/>
+      <c r="H26" s="80" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="47"/>
+      <c r="H27" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="44"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="47"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="47"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="45"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="47"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="47"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="H4:L7"/>
+    <mergeCell ref="H10:L19"/>
+    <mergeCell ref="H22:L25"/>
+    <mergeCell ref="H27:L31"/>
+    <mergeCell ref="B16:F31"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2123,7 +3753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2145,16 +3775,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776567A7-D8E9-40E1-82FD-FF3EE741B0B4}">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Y134"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="24" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="23" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2164,61 +3794,61 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="34"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="70"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="73"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="40"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="76"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="22" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="20" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2237,408 +3867,1125 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="3:17" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C20" s="44" t="s">
+    <row r="20" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="C20" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="3:17" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C21" s="30" t="s">
+    <row r="21" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="C21" s="20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="3:17" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C22" s="43" t="s">
+    <row r="22" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="C22" s="25" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="3:17" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="C24" s="43" t="s">
+    <row r="24" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="C24" s="25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C26" s="41" t="s">
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C26" s="23" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C27" s="45" t="s">
+      <c r="H26" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C27" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="52"/>
+      <c r="E27" s="53"/>
+      <c r="G27" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
+      <c r="K27" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="O27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="53"/>
+      <c r="S27" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="T27" s="52"/>
+      <c r="U27" s="53"/>
+      <c r="W27" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="53"/>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C28" s="54"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="56"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="56"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="56"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="56"/>
+      <c r="W28" s="54"/>
+      <c r="X28" s="55"/>
+      <c r="Y28" s="56"/>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C29" s="54"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="56"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="56"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="56"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="56"/>
+      <c r="W29" s="54"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="56"/>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C30" s="54"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="56"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="56"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="56"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="56"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="56"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="55"/>
+      <c r="Y30" s="56"/>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C31" s="54"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="56"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="56"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="56"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="56"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="56"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="55"/>
+      <c r="Y31" s="56"/>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C32" s="57"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="59"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="59"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="59"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="59"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="59"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="58"/>
+      <c r="Y32" s="59"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C34" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="G27" s="45" t="s">
+      <c r="D34" s="52"/>
+      <c r="E34" s="53"/>
+      <c r="G34" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="K27" s="45" t="s">
+      <c r="H34" s="52"/>
+      <c r="I34" s="53"/>
+      <c r="K34" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="L27" s="46"/>
-      <c r="M27" s="47"/>
-      <c r="O27" s="45" t="s">
+      <c r="L34" s="52"/>
+      <c r="M34" s="53"/>
+      <c r="O34" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="47"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C28" s="48"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="50"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="50"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C30" s="48"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="50"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="50"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="50"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="50"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="50"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C32" s="51"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="53"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="53"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="53"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="53"/>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C34" s="45" t="s">
+      <c r="P34" s="52"/>
+      <c r="Q34" s="53"/>
+      <c r="S34" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
-      <c r="G34" s="45" t="s">
+      <c r="T34" s="52"/>
+      <c r="U34" s="53"/>
+      <c r="W34" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C35" s="48"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="50"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="50"/>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C36" s="48"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-    </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C37" s="48"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-    </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C38" s="48"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C39" s="51"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="53"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="53"/>
-    </row>
-    <row r="43" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C43" s="21" t="s">
+      <c r="X34" s="52"/>
+      <c r="Y34" s="53"/>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C35" s="54"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="56"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="56"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="56"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="56"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="55"/>
+      <c r="U35" s="56"/>
+      <c r="W35" s="54"/>
+      <c r="X35" s="55"/>
+      <c r="Y35" s="56"/>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C36" s="54"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="56"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="56"/>
+      <c r="S36" s="54"/>
+      <c r="T36" s="55"/>
+      <c r="U36" s="56"/>
+      <c r="W36" s="54"/>
+      <c r="X36" s="55"/>
+      <c r="Y36" s="56"/>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C37" s="54"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="56"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="56"/>
+      <c r="S37" s="54"/>
+      <c r="T37" s="55"/>
+      <c r="U37" s="56"/>
+      <c r="W37" s="54"/>
+      <c r="X37" s="55"/>
+      <c r="Y37" s="56"/>
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C38" s="54"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="56"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="56"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="55"/>
+      <c r="Q38" s="56"/>
+      <c r="S38" s="54"/>
+      <c r="T38" s="55"/>
+      <c r="U38" s="56"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="55"/>
+      <c r="Y38" s="56"/>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C39" s="57"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="59"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="59"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="59"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="59"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="58"/>
+      <c r="Y39" s="59"/>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C43" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="23"/>
-      <c r="G43" s="21" t="s">
+      <c r="D43" s="43"/>
+      <c r="E43" s="44"/>
+      <c r="G43" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="H43" s="22"/>
-      <c r="I43" s="23"/>
-    </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C44" s="24"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="26"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="26"/>
-    </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="26"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="26"/>
-    </row>
-    <row r="46" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C46" s="24"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="26"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="26"/>
-    </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C47" s="24"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="26"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="26"/>
-    </row>
-    <row r="48" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C48" s="27"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="29"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="29"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C50" s="45" t="s">
+      <c r="H43" s="43"/>
+      <c r="I43" s="44"/>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C44" s="45"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="47"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="47"/>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C45" s="45"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="47"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="47"/>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C46" s="45"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="47"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="47"/>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C47" s="45"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="47"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="47"/>
+    </row>
+    <row r="48" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C48" s="48"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="50"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="50"/>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C50" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D50" s="46"/>
-      <c r="E50" s="47"/>
-      <c r="G50" s="45" t="s">
+      <c r="D50" s="52"/>
+      <c r="E50" s="53"/>
+      <c r="G50" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="H50" s="46"/>
-      <c r="I50" s="47"/>
-      <c r="K50" s="45" t="s">
+      <c r="H50" s="52"/>
+      <c r="I50" s="53"/>
+      <c r="K50" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="L50" s="46"/>
-      <c r="M50" s="47"/>
-      <c r="O50" s="45" t="s">
+      <c r="L50" s="52"/>
+      <c r="M50" s="53"/>
+      <c r="O50" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="47"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C51" s="48"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="50"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="50"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="49"/>
-      <c r="M51" s="50"/>
-      <c r="O51" s="48"/>
-      <c r="P51" s="49"/>
-      <c r="Q51" s="50"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C52" s="48"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="50"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="50"/>
-      <c r="K52" s="48"/>
-      <c r="L52" s="49"/>
-      <c r="M52" s="50"/>
-      <c r="O52" s="48"/>
-      <c r="P52" s="49"/>
-      <c r="Q52" s="50"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C53" s="48"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="50"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="50"/>
-      <c r="K53" s="48"/>
-      <c r="L53" s="49"/>
-      <c r="M53" s="50"/>
-      <c r="O53" s="48"/>
-      <c r="P53" s="49"/>
-      <c r="Q53" s="50"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C54" s="48"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="50"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="50"/>
-      <c r="K54" s="48"/>
-      <c r="L54" s="49"/>
-      <c r="M54" s="50"/>
-      <c r="O54" s="48"/>
-      <c r="P54" s="49"/>
-      <c r="Q54" s="50"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C55" s="51"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="53"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="53"/>
-      <c r="K55" s="51"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="53"/>
-      <c r="O55" s="51"/>
-      <c r="P55" s="52"/>
-      <c r="Q55" s="53"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C57" s="45" t="s">
+      <c r="P50" s="52"/>
+      <c r="Q50" s="53"/>
+      <c r="S50" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="46"/>
-      <c r="E57" s="47"/>
-      <c r="G57" s="45" t="s">
+      <c r="T50" s="52"/>
+      <c r="U50" s="53"/>
+      <c r="W50" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="H57" s="46"/>
-      <c r="I57" s="47"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C58" s="48"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="50"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="50"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C59" s="48"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="50"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="50"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C60" s="48"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="50"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="50"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C61" s="48"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="50"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="50"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
-      <c r="C62" s="51"/>
-      <c r="D62" s="52"/>
-      <c r="E62" s="53"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="53"/>
+      <c r="X50" s="52"/>
+      <c r="Y50" s="53"/>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C51" s="54"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="56"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="56"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="56"/>
+      <c r="O51" s="54"/>
+      <c r="P51" s="55"/>
+      <c r="Q51" s="56"/>
+      <c r="S51" s="54"/>
+      <c r="T51" s="55"/>
+      <c r="U51" s="56"/>
+      <c r="W51" s="54"/>
+      <c r="X51" s="55"/>
+      <c r="Y51" s="56"/>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C52" s="54"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="56"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="56"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="56"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="56"/>
+      <c r="S52" s="54"/>
+      <c r="T52" s="55"/>
+      <c r="U52" s="56"/>
+      <c r="W52" s="54"/>
+      <c r="X52" s="55"/>
+      <c r="Y52" s="56"/>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="56"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="56"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="56"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="55"/>
+      <c r="Q53" s="56"/>
+      <c r="S53" s="54"/>
+      <c r="T53" s="55"/>
+      <c r="U53" s="56"/>
+      <c r="W53" s="54"/>
+      <c r="X53" s="55"/>
+      <c r="Y53" s="56"/>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C54" s="54"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="56"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="56"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="56"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="55"/>
+      <c r="Q54" s="56"/>
+      <c r="S54" s="54"/>
+      <c r="T54" s="55"/>
+      <c r="U54" s="56"/>
+      <c r="W54" s="54"/>
+      <c r="X54" s="55"/>
+      <c r="Y54" s="56"/>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C55" s="57"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="59"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="59"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="59"/>
+      <c r="O55" s="57"/>
+      <c r="P55" s="58"/>
+      <c r="Q55" s="59"/>
+      <c r="S55" s="57"/>
+      <c r="T55" s="58"/>
+      <c r="U55" s="59"/>
+      <c r="W55" s="57"/>
+      <c r="X55" s="58"/>
+      <c r="Y55" s="59"/>
+    </row>
+    <row r="67" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B68" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="C68" s="61"/>
+      <c r="D68" s="62"/>
+      <c r="F68" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" s="43"/>
+      <c r="H68" s="44"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B69" s="63"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="65"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="47"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B70" s="63"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="F70" s="45"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="47"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B71" s="63"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="65"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="47"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B72" s="63"/>
+      <c r="C72" s="64"/>
+      <c r="D72" s="65"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="47"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B73" s="66"/>
+      <c r="C73" s="67"/>
+      <c r="D73" s="68"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="50"/>
+    </row>
+    <row r="75" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A75" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B76" s="42"/>
+      <c r="C76" s="43"/>
+      <c r="D76" s="44"/>
+      <c r="F76" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G76" s="43"/>
+      <c r="H76" s="44"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B77" s="45"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="47"/>
+      <c r="F77" s="45"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="47"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B78" s="45"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="47"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="47"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B79" s="45"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="47"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="47"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B80" s="45"/>
+      <c r="C80" s="46"/>
+      <c r="D80" s="47"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="47"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B81" s="48"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="50"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="50"/>
+    </row>
+    <row r="85" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A85" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>93</v>
+      </c>
+      <c r="F86" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B87" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="43"/>
+      <c r="D87" s="44"/>
+      <c r="F87" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="G87" s="43"/>
+      <c r="H87" s="44"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B88" s="45"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="47"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="47"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B89" s="45"/>
+      <c r="C89" s="46"/>
+      <c r="D89" s="47"/>
+      <c r="F89" s="45"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="47"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B90" s="45"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="47"/>
+      <c r="E90" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" s="45"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="47"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B91" s="45"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="47"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="47"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B92" s="45"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="47"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="46"/>
+      <c r="H92" s="47"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B93" s="45"/>
+      <c r="C93" s="46"/>
+      <c r="D93" s="47"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="46"/>
+      <c r="H93" s="47"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B94" s="48"/>
+      <c r="C94" s="49"/>
+      <c r="D94" s="50"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="49"/>
+      <c r="H94" s="50"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A98" s="29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="81" t="s">
+        <v>189</v>
+      </c>
+      <c r="F99" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="J99" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B101" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="52"/>
+      <c r="D101" s="53"/>
+      <c r="F101" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="G101" s="52"/>
+      <c r="H101" s="53"/>
+      <c r="J101" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="K101" s="43"/>
+      <c r="L101" s="44"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B102" s="57"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="59"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="59"/>
+      <c r="J102" s="45"/>
+      <c r="K102" s="46"/>
+      <c r="L102" s="47"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
+      <c r="D103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
+      <c r="J103" s="45"/>
+      <c r="K103" s="46"/>
+      <c r="L103" s="47"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B104" t="s">
+        <v>204</v>
+      </c>
+      <c r="F104" t="s">
+        <v>204</v>
+      </c>
+      <c r="J104" s="45"/>
+      <c r="K104" s="46"/>
+      <c r="L104" s="47"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B105" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" s="43"/>
+      <c r="D105" s="44"/>
+      <c r="F105" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="G105" s="43"/>
+      <c r="H105" s="44"/>
+      <c r="J105" s="45"/>
+      <c r="K105" s="46"/>
+      <c r="L105" s="47"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B106" s="45"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="47"/>
+      <c r="F106" s="45"/>
+      <c r="G106" s="46"/>
+      <c r="H106" s="47"/>
+      <c r="J106" s="45"/>
+      <c r="K106" s="46"/>
+      <c r="L106" s="47"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B107" s="45"/>
+      <c r="C107" s="46"/>
+      <c r="D107" s="47"/>
+      <c r="F107" s="45"/>
+      <c r="G107" s="46"/>
+      <c r="H107" s="47"/>
+      <c r="J107" s="45"/>
+      <c r="K107" s="46"/>
+      <c r="L107" s="47"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B108" s="45"/>
+      <c r="C108" s="46"/>
+      <c r="D108" s="47"/>
+      <c r="F108" s="45"/>
+      <c r="G108" s="46"/>
+      <c r="H108" s="47"/>
+      <c r="J108" s="45"/>
+      <c r="K108" s="46"/>
+      <c r="L108" s="47"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B109" s="45"/>
+      <c r="C109" s="46"/>
+      <c r="D109" s="47"/>
+      <c r="F109" s="45"/>
+      <c r="G109" s="46"/>
+      <c r="H109" s="47"/>
+      <c r="J109" s="45"/>
+      <c r="K109" s="46"/>
+      <c r="L109" s="47"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B110" s="45"/>
+      <c r="C110" s="46"/>
+      <c r="D110" s="47"/>
+      <c r="F110" s="45"/>
+      <c r="G110" s="46"/>
+      <c r="H110" s="47"/>
+      <c r="J110" s="48"/>
+      <c r="K110" s="49"/>
+      <c r="L110" s="50"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B111" s="45"/>
+      <c r="C111" s="46"/>
+      <c r="D111" s="47"/>
+      <c r="E111" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F111" s="45"/>
+      <c r="G111" s="46"/>
+      <c r="H111" s="47"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B112" s="45"/>
+      <c r="C112" s="46"/>
+      <c r="D112" s="47"/>
+      <c r="F112" s="45"/>
+      <c r="G112" s="46"/>
+      <c r="H112" s="47"/>
+      <c r="J112" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B113" s="45"/>
+      <c r="C113" s="46"/>
+      <c r="D113" s="47"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="46"/>
+      <c r="H113" s="47"/>
+      <c r="K113" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B114" s="45"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="47"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="46"/>
+      <c r="H114" s="47"/>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B115" s="45"/>
+      <c r="C115" s="46"/>
+      <c r="D115" s="47"/>
+      <c r="F115" s="45"/>
+      <c r="G115" s="46"/>
+      <c r="H115" s="47"/>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B116" s="45"/>
+      <c r="C116" s="46"/>
+      <c r="D116" s="47"/>
+      <c r="F116" s="45"/>
+      <c r="G116" s="46"/>
+      <c r="H116" s="47"/>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B117" s="45"/>
+      <c r="C117" s="46"/>
+      <c r="D117" s="47"/>
+      <c r="F117" s="45"/>
+      <c r="G117" s="46"/>
+      <c r="H117" s="47"/>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B118" s="48"/>
+      <c r="C118" s="49"/>
+      <c r="D118" s="50"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="49"/>
+      <c r="H118" s="50"/>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>200</v>
+      </c>
+      <c r="F120" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B121" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C121" s="43"/>
+      <c r="D121" s="44"/>
+      <c r="F121" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="G121" s="43"/>
+      <c r="H121" s="44"/>
+      <c r="J121" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="K121" s="43"/>
+      <c r="L121" s="44"/>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B122" s="45"/>
+      <c r="C122" s="46"/>
+      <c r="D122" s="47"/>
+      <c r="F122" s="45"/>
+      <c r="G122" s="46"/>
+      <c r="H122" s="47"/>
+      <c r="J122" s="45"/>
+      <c r="K122" s="46"/>
+      <c r="L122" s="47"/>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B123" s="45"/>
+      <c r="C123" s="46"/>
+      <c r="D123" s="47"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="46"/>
+      <c r="H123" s="47"/>
+      <c r="J123" s="45"/>
+      <c r="K123" s="46"/>
+      <c r="L123" s="47"/>
+    </row>
+    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B124" s="45"/>
+      <c r="C124" s="46"/>
+      <c r="D124" s="47"/>
+      <c r="F124" s="45"/>
+      <c r="G124" s="46"/>
+      <c r="H124" s="47"/>
+      <c r="J124" s="45"/>
+      <c r="K124" s="46"/>
+      <c r="L124" s="47"/>
+    </row>
+    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B125" s="45"/>
+      <c r="C125" s="46"/>
+      <c r="D125" s="47"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="46"/>
+      <c r="H125" s="47"/>
+      <c r="J125" s="45"/>
+      <c r="K125" s="46"/>
+      <c r="L125" s="47"/>
+    </row>
+    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B126" s="45"/>
+      <c r="C126" s="46"/>
+      <c r="D126" s="47"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="47"/>
+      <c r="J126" s="45"/>
+      <c r="K126" s="46"/>
+      <c r="L126" s="47"/>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B127" s="45"/>
+      <c r="C127" s="46"/>
+      <c r="D127" s="47"/>
+      <c r="E127" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F127" s="45"/>
+      <c r="G127" s="46"/>
+      <c r="H127" s="47"/>
+      <c r="J127" s="45"/>
+      <c r="K127" s="46"/>
+      <c r="L127" s="47"/>
+    </row>
+    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B128" s="45"/>
+      <c r="C128" s="46"/>
+      <c r="D128" s="47"/>
+      <c r="F128" s="45"/>
+      <c r="G128" s="46"/>
+      <c r="H128" s="47"/>
+      <c r="J128" s="45"/>
+      <c r="K128" s="46"/>
+      <c r="L128" s="47"/>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B129" s="45"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="47"/>
+      <c r="F129" s="45"/>
+      <c r="G129" s="46"/>
+      <c r="H129" s="47"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="49"/>
+      <c r="L129" s="50"/>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B130" s="45"/>
+      <c r="C130" s="46"/>
+      <c r="D130" s="47"/>
+      <c r="F130" s="45"/>
+      <c r="G130" s="46"/>
+      <c r="H130" s="47"/>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B131" s="45"/>
+      <c r="C131" s="46"/>
+      <c r="D131" s="47"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="46"/>
+      <c r="H131" s="47"/>
+      <c r="J131" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B132" s="45"/>
+      <c r="C132" s="46"/>
+      <c r="D132" s="47"/>
+      <c r="F132" s="45"/>
+      <c r="G132" s="46"/>
+      <c r="H132" s="47"/>
+      <c r="K132" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B133" s="45"/>
+      <c r="C133" s="46"/>
+      <c r="D133" s="47"/>
+      <c r="F133" s="45"/>
+      <c r="G133" s="46"/>
+      <c r="H133" s="47"/>
+      <c r="K133" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B134" s="48"/>
+      <c r="C134" s="49"/>
+      <c r="D134" s="50"/>
+      <c r="F134" s="48"/>
+      <c r="G134" s="49"/>
+      <c r="H134" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="35">
+    <mergeCell ref="B121:D134"/>
+    <mergeCell ref="F121:H134"/>
+    <mergeCell ref="J121:L129"/>
+    <mergeCell ref="S50:U55"/>
+    <mergeCell ref="W50:Y55"/>
+    <mergeCell ref="B105:D118"/>
+    <mergeCell ref="F105:H118"/>
+    <mergeCell ref="B101:D102"/>
+    <mergeCell ref="F101:H102"/>
+    <mergeCell ref="J101:L110"/>
+    <mergeCell ref="C4:H7"/>
     <mergeCell ref="C34:E39"/>
-    <mergeCell ref="G34:I39"/>
-    <mergeCell ref="K50:M55"/>
-    <mergeCell ref="O50:Q55"/>
-    <mergeCell ref="C57:E62"/>
-    <mergeCell ref="G57:I62"/>
-    <mergeCell ref="C4:H7"/>
-    <mergeCell ref="C27:E32"/>
     <mergeCell ref="G50:I55"/>
     <mergeCell ref="C50:E55"/>
     <mergeCell ref="C43:E48"/>
     <mergeCell ref="G43:I48"/>
+    <mergeCell ref="G34:I39"/>
+    <mergeCell ref="C27:E32"/>
     <mergeCell ref="G27:I32"/>
+    <mergeCell ref="B87:D94"/>
+    <mergeCell ref="F87:H94"/>
+    <mergeCell ref="S34:U39"/>
+    <mergeCell ref="W34:Y39"/>
     <mergeCell ref="K27:M32"/>
     <mergeCell ref="O27:Q32"/>
+    <mergeCell ref="S27:U32"/>
+    <mergeCell ref="W27:Y32"/>
+    <mergeCell ref="B76:D81"/>
+    <mergeCell ref="K34:M39"/>
+    <mergeCell ref="O34:Q39"/>
+    <mergeCell ref="B68:D73"/>
+    <mergeCell ref="F76:H81"/>
+    <mergeCell ref="F68:H73"/>
+    <mergeCell ref="K50:M55"/>
+    <mergeCell ref="O50:Q55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2647,6 +4994,261 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84513203-8B75-439A-83DC-F0433279F24C}">
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="A1" s="32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B2" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B3" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B4" s="35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B5" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B6" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B9" s="34"/>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B10" s="33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B12" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="34"/>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B14" s="33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B18" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B26" s="35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="B35" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+    </row>
+    <row r="37" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B37" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="H37" s="36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B38" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B39" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B40" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="B42" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B43" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B44" s="33" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B45" s="33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B46" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B48" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2656,7 +5258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2666,7 +5268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2711,8 +5313,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="3"/>
@@ -3072,17 +5678,264 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="N2:U28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="N2" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O3" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="44"/>
+    </row>
+    <row r="4" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O4" s="45"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="47"/>
+    </row>
+    <row r="5" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O5" s="45"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="47"/>
+    </row>
+    <row r="6" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O6" s="45"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="47"/>
+    </row>
+    <row r="7" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O7" s="45"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="47"/>
+    </row>
+    <row r="8" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O8" s="45"/>
+      <c r="P8" s="77"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="47"/>
+    </row>
+    <row r="9" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O9" s="45"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="77"/>
+      <c r="U9" s="47"/>
+    </row>
+    <row r="10" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O10" s="48"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+    </row>
+    <row r="11" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="N11" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O12" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="44"/>
+    </row>
+    <row r="13" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O13" s="45"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="77"/>
+      <c r="U13" s="47"/>
+    </row>
+    <row r="14" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O14" s="45"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="77"/>
+      <c r="U14" s="47"/>
+    </row>
+    <row r="15" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O15" s="45"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="77"/>
+      <c r="U15" s="47"/>
+    </row>
+    <row r="16" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O16" s="45"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="77"/>
+      <c r="U16" s="47"/>
+    </row>
+    <row r="17" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O17" s="45"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="77"/>
+      <c r="S17" s="77"/>
+      <c r="T17" s="77"/>
+      <c r="U17" s="47"/>
+    </row>
+    <row r="18" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O18" s="45"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="77"/>
+      <c r="R18" s="77"/>
+      <c r="S18" s="77"/>
+      <c r="T18" s="77"/>
+      <c r="U18" s="47"/>
+    </row>
+    <row r="19" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O19" s="48"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="50"/>
+    </row>
+    <row r="20" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="N20" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O21" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="44"/>
+    </row>
+    <row r="22" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O22" s="45"/>
+      <c r="P22" s="77"/>
+      <c r="Q22" s="77"/>
+      <c r="R22" s="77"/>
+      <c r="S22" s="77"/>
+      <c r="T22" s="77"/>
+      <c r="U22" s="47"/>
+    </row>
+    <row r="23" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O23" s="45"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="77"/>
+      <c r="R23" s="77"/>
+      <c r="S23" s="77"/>
+      <c r="T23" s="77"/>
+      <c r="U23" s="47"/>
+    </row>
+    <row r="24" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O24" s="45"/>
+      <c r="P24" s="77"/>
+      <c r="Q24" s="77"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="77"/>
+      <c r="T24" s="77"/>
+      <c r="U24" s="47"/>
+    </row>
+    <row r="25" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O25" s="45"/>
+      <c r="P25" s="77"/>
+      <c r="Q25" s="77"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="77"/>
+      <c r="T25" s="77"/>
+      <c r="U25" s="47"/>
+    </row>
+    <row r="26" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O26" s="45"/>
+      <c r="P26" s="77"/>
+      <c r="Q26" s="77"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="77"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="47"/>
+    </row>
+    <row r="27" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O27" s="45"/>
+      <c r="P27" s="77"/>
+      <c r="Q27" s="77"/>
+      <c r="R27" s="77"/>
+      <c r="S27" s="77"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="47"/>
+    </row>
+    <row r="28" spans="14:21" x14ac:dyDescent="0.2">
+      <c r="O28" s="48"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="O3:U10"/>
+    <mergeCell ref="O12:U19"/>
+    <mergeCell ref="O21:U28"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3090,14 +5943,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
+++ b/40_数据库/学习笔记_RDBMS_KingbaseES.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7452DE-5C93-4631-9215-80F241EEE1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A8E08-14E5-43C8-ACB9-2573B12848DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="311">
   <si>
     <r>
       <rPr>
@@ -586,10 +586,6 @@
   <si>
     <t>在金仓数据库中执行报错：SQL 错误 [42601]: ERROR: syntax error at or near "pctfree"
   Position: 611 At Line: 18, Line Position: 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表结构迁移</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2179,12 +2175,2841 @@
     <t>Oracle原栈和队列自定义数据类型转换：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Max(p.rowid::text)</t>
+  </si>
+  <si>
+    <t>Max(p.rowid)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT *</t>
+  </si>
+  <si>
+    <t>FROM UNNEST(STRING_TO_ARRAY('111,222', ',')) AS w(column_value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHERE w.column_value='111' </t>
+  </si>
+  <si>
+    <t>将分隔字符转成表并查询是否存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oralce查询，并导出为csv文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：时间戳列字段需要查询时转换为字符，再导出为csv文件。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select ritem_id,
+       ritem_code,
+       ritem_name,
+       ritem_sqldef,
+       ritem_remark,
+       ritem_editwhere,
+       ritem_querywhere,
+       ritem_statisticswhere,
+       creater,
+      TO_CHAR(creat_time,'yyyy-MM-dd HH24:mi:ss') as creat_time,
+      modifyer,
+      TO_CHAR(modify_time,'yyyy-MM-dd HH24:mi:ss') modify_time,
+      ritem_type
+  from dp_sys_t_resourceitem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbeaver：导入数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在DBeaver中导入时，表映射中映射规则中，名称大小写要选择【小写】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、表结构迁移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、表数据迁移：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle包转换为KingbaseES中的包：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用KSQL Developer工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、创建一个空的同名新包：包名会自动转为小写。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、在【程序包】中右击刚刚创建的那个包 》生成SQL 》 DDL 》打开编辑器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作步骤：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、修改内容（分别从旧Oracle中复制包的声明和包体，然后粘贴），然后执行即可。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、一些常见的编译报错的修改点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要有两种思路：一种是利用专门的性能分析插件进行细粒度分析，另一种是启用SQL监控或日志来捕获执行信息。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>KingbaseES</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Oracle</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>兼容模式下测试包中存储过程的每段</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>执行时间</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>方案一：使用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>plsql_plprofiler</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 插件（推荐，最详细）</t>
+    </r>
+  </si>
+  <si>
+    <t>操作步骤如下：</t>
+  </si>
+  <si>
+    <r>
+      <t>plsql_plprofiler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> 是KingbaseES官方提供的PL/SQL性能分析利器。它能精确到代码每一行，清晰地展示每条SQL的执行次数、总耗时和最长耗时，非常适合定位存储过程或包中的性能瓶颈。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> EXTENSION plsql_plprofiler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. 创建插件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（通常只需执行一次）：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>准备测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：确保你的包（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）和其中的存储过程已正确创建。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开启分析并执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-- 1. 清理本地和全局的旧数据，确保结果准确</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> pl_profiler_reset_local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> pl_profiler_reset_shared</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 2. 启动当前会话的分析器</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> pl_profiler_set_enabled_local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 3. 执行你想要测试的包中的存储过程</t>
+  </si>
+  <si>
+    <t>-- 假设你的包名为 my_package，过程名为 test_proc</t>
+  </si>
+  <si>
+    <r>
+      <t>CALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> my_package</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>test_proc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 4. 关闭分析器</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> pl_profiler_set_enabled_local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 5. 收集数据</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> pl_profiler_collect_data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>运行以下查询，你将得到一张详细的报告，包含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>每一行代码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>的执行统计。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>查看分析结果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">func_oid::regproc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> funcname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>line_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>exec_count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>bigint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> exec_count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>total_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>bigint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> total_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFA0A1A7"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 总时间（微秒）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>MAX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>longest_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>bigint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> longest_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFA0A1A7"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 单次最长执行时间（微秒）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>source</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    pl_profiler_linestats_shared</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    pl_profiler_funcs_source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pl_profiler_func_oids_shared</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>())</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> S </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">func_oid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">func_oid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">line_number </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>line_number</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>func_oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>line_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>source</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>func_oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>line_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>注意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>total_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 和 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>longest_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 的单位是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>微秒 (μs)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>方案二：使用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 插件（适合日志分析）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>如果你想将每条SQL的执行计划和耗时都记录到数据库日志中，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 插件是很好的选择</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.加载插件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：在 kingbase.conf 文件中添加 auto_explain 到 shared_preload_libraries，然后重启数据库。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shared_preload_libraries = 'auto_explain'</t>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> client_min_messages </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'log'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">log_min_duration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFA0A1A7"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 记录所有SQL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">log_analyze </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFA0A1A7"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 包含实际执行时间等</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">log_verbose </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">log_buffers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> auto_explain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">log_nested_statements </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFB76B01"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFA0A1A7"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 关键：记录过程内部的SQL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2.会话级开启详细日志</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（避免影响全局性能）：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.执行存储过程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.查看日志</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：执行完毕后，在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>KingbaseES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的日志文件中，你会看到类似下面的记录，清晰地标明了每条</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及其执行时间（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>duration</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOG: duration: 1.825 ms  plan: ... (SQL 1)</t>
+  </si>
+  <si>
+    <t>LOG: duration: 1.876 ms  plan: ... (SQL 2)</t>
+  </si>
+  <si>
+    <t>LOG: duration: 27710.539 ms  plan: ... (SQL 3)</t>
+  </si>
+  <si>
+    <r>
+      <t>方案三：使用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SQL监控</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 功能（适合监控长耗时SQL）</t>
+    </r>
+  </si>
+  <si>
+    <t>KingbaseES提供了内置的SQL监控功能，可以自动捕获执行时间较长的SQL</t>
+  </si>
+  <si>
+    <r>
+      <t>前置配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>kingbase.conf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 中配置并重启数据库</t>
+    </r>
+  </si>
+  <si>
+    <t>shared_preload_libraries = 'plsql, sys_stat_statements, sys_sqltune'</t>
+  </si>
+  <si>
+    <t>sql_monitor.track = 'all'</t>
+  </si>
+  <si>
+    <t>然后创建扩展：</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> EXTENSION sys_sqltune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. 执行存储过程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：正常调用你的存储过程。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 查看监控结果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：</t>
+    </r>
+  </si>
+  <si>
+    <t>可以通过以下视图查看：</t>
+  </si>
+  <si>
+    <r>
+      <t>SQL被监控的条件是：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单次执行消耗超过5秒的CPU或I/O时间，或使用了/*+ MONITOR */ hint。</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 查看被监控的SQL整体统计</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> V$SQL_MONITOR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> last_ts </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DESC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>-- 查看执行计划的详细节点统计</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> V$SQL_PLAN_MONITOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>也可以生成监控报告：</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> DBMS_SQL_MONITOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>REPORT_SQL_MONITOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'TEXT'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>方案四：使用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sys_stat_dbtime</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 视图（全局视角）</t>
+    </r>
+  </si>
+  <si>
+    <t>这个视图提供了数据库时间的宏观分解，可以帮你从全局了解时间消耗在解析、执行、编译等哪个环节</t>
+  </si>
+  <si>
+    <r>
+      <t>开启参数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>kingbase.conf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 中设置并重启</t>
+    </r>
+  </si>
+  <si>
+    <t>track_sql = on</t>
+  </si>
+  <si>
+    <t>track_instance = on</t>
+  </si>
+  <si>
+    <r>
+      <t>执行与查看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>：执行完存储过程后，查询该视图。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> sys_stat_dbtime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>结果会显示如 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Parse Event（解析）、Execute Event（执行）、PLSQL Execute（PL/SQL执行）等各项的累计耗时。</t>
+    </r>
+  </si>
+  <si>
+    <t>其他辅助方法</t>
+  </si>
+  <si>
+    <r>
+      <t>\timing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> 命令：在ksql命令行工具中，使用 \timing on 可以测量整个命令（如CALL语句）的总耗时。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXPLAIN ANALYZE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：如果你想单独分析包中某个复杂的SQL语句，可以将其提取出来，使用 EXPLAIN ANALYZE 查看其详细的执行计划和实际耗时</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2458,6 +5283,110 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFA626A4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF383A42"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFA0A1A7"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFB76B01"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4078F2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF50A14F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2479,7 +5408,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2582,11 +5511,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2680,6 +5646,21 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2693,12 +5674,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2737,6 +5721,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2764,41 +5772,67 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2845,6 +5879,286 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>39955</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6181725" cy="6398945"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453D24A3-4D43-4696-BF0E-79AEE1B63D4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="457200" y="9345880"/>
+          <a:ext cx="6181725" cy="6398945"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>135391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>647699</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF728309-29E7-4B3B-9B80-83E0E83E01AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="457199" y="4193041"/>
+          <a:ext cx="4886325" cy="4769984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>162509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{920888A9-D3E7-4B94-A0A3-A0FEBB11A71E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5695950" y="3315284"/>
+          <a:ext cx="5505450" cy="5714416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>99883</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{740D8FB6-E9BA-4D3F-BC91-0056E4859B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11529883" y="3305174"/>
+          <a:ext cx="5519866" cy="5705475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3190,7 +6504,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E1" s="19" t="s">
         <v>52</v>
@@ -3260,7 +6574,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="16" t="s">
@@ -3271,7 +6585,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="41"/>
+      <c r="B25" s="50"/>
       <c r="C25" s="18" t="s">
         <v>24</v>
       </c>
@@ -3280,7 +6594,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="50" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="16" t="s">
@@ -3291,7 +6605,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="41"/>
+      <c r="B27" s="50"/>
       <c r="C27" s="18" t="s">
         <v>50</v>
       </c>
@@ -3300,7 +6614,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -3311,7 +6625,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="41"/>
+      <c r="B29" s="50"/>
       <c r="C29" s="18" t="s">
         <v>32</v>
       </c>
@@ -3320,7 +6634,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="50" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -3331,7 +6645,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B31" s="41"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="17" t="s">
         <v>37</v>
       </c>
@@ -3340,7 +6654,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="50" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="16" t="s">
@@ -3351,7 +6665,7 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B33" s="41"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="17" t="s">
         <v>42</v>
       </c>
@@ -3360,7 +6674,7 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="50" t="s">
         <v>45</v>
       </c>
       <c r="C34" s="16" t="s">
@@ -3371,7 +6685,7 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B35" s="41"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="18" t="s">
         <v>47</v>
       </c>
@@ -3401,321 +6715,321 @@
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H3" s="80" t="s">
-        <v>101</v>
+        <v>176</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44"/>
+        <v>177</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="53"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="47"/>
+        <v>181</v>
+      </c>
+      <c r="H5" s="57"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="56"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>181</v>
-      </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="47"/>
+        <v>180</v>
+      </c>
+      <c r="H6" s="57"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="56"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="50"/>
+        <v>178</v>
+      </c>
+      <c r="H7" s="58"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="60"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="78" t="s">
-        <v>183</v>
+      <c r="B8" s="41" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="80" t="s">
-        <v>103</v>
+      <c r="H9" s="43" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="57"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="56"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="H12" s="57"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="56"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="57"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="56"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="57"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="56"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="57"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="56"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="56"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="57"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="56"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="57"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="56"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="56"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="57"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="56"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="60"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="57"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="56"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="57"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="56"/>
+      <c r="H21" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="78" t="s">
-        <v>184</v>
-      </c>
-      <c r="H11" s="45"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="47"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="78" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="45"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="47"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="78" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="47"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="45"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="47"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="79" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="47"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="47"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="45"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="47"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="47"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="47"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="50"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="47"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" s="45"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="47"/>
-      <c r="H21" s="80" t="s">
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="57"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="56"/>
+      <c r="H22" s="51" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="47"/>
-      <c r="H22" s="42" t="s">
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="53"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="57"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="56"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="57"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="56"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="57"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="56"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="60"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="57"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="56"/>
+      <c r="H26" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="47"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="47"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="47"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="50"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="47"/>
-      <c r="H26" s="80" t="s">
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="57"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="56"/>
+      <c r="H27" s="51" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="47"/>
-      <c r="H27" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="44"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="53"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="47"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="47"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="56"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="47"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="56"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="56"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="45"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="47"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="47"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="56"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="56"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="50"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3775,7 +7089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776567A7-D8E9-40E1-82FD-FF3EE741B0B4}">
-  <dimension ref="A1:Y134"/>
+  <dimension ref="A1:Y222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
@@ -3785,7 +7099,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" s="23" t="s">
-        <v>56</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -3794,17 +7108,17 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C5" s="71"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="72"/>
       <c r="E5" s="72"/>
       <c r="F5" s="72"/>
@@ -3812,7 +7126,7 @@
       <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C6" s="71"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="72"/>
       <c r="E6" s="72"/>
       <c r="F6" s="72"/>
@@ -3829,1138 +7143,1314 @@
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="C9" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C10" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C11" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C12" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C20" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C22" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="3:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="C24" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C27" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="62"/>
+      <c r="E27" s="63"/>
+      <c r="G27" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="62"/>
+      <c r="I27" s="63"/>
+      <c r="K27" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="O27" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="63"/>
+      <c r="S27" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="T27" s="62"/>
+      <c r="U27" s="63"/>
+      <c r="W27" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="X27" s="62"/>
+      <c r="Y27" s="63"/>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C28" s="64"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="66"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="66"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="66"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="66"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="66"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="66"/>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="66"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="66"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="66"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="66"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="66"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="66"/>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="66"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="66"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="66"/>
+      <c r="S30" s="64"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="66"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="66"/>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C31" s="64"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="66"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="66"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="66"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="66"/>
+      <c r="S31" s="64"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="66"/>
+      <c r="W31" s="64"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="66"/>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C32" s="67"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="69"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="69"/>
+      <c r="K32" s="67"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="69"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="68"/>
+      <c r="Q32" s="69"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="69"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="69"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C34" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="62"/>
+      <c r="E34" s="63"/>
+      <c r="G34" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="62"/>
+      <c r="I34" s="63"/>
+      <c r="K34" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="L34" s="62"/>
+      <c r="M34" s="63"/>
+      <c r="O34" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="63"/>
+      <c r="S34" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="T34" s="62"/>
+      <c r="U34" s="63"/>
+      <c r="W34" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="63"/>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C35" s="64"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="66"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="66"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="66"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="66"/>
+      <c r="S35" s="64"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="66"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="66"/>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C36" s="64"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="66"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="66"/>
+      <c r="K36" s="64"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="66"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="66"/>
+      <c r="S36" s="64"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="66"/>
+      <c r="W36" s="64"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="66"/>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="66"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="66"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="66"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="66"/>
+      <c r="S37" s="64"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="66"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="66"/>
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="66"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="66"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="66"/>
+      <c r="O38" s="64"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="66"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="66"/>
+      <c r="W38" s="64"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="66"/>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="69"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="69"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="68"/>
+      <c r="M39" s="69"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="69"/>
+      <c r="S39" s="67"/>
+      <c r="T39" s="68"/>
+      <c r="U39" s="69"/>
+      <c r="W39" s="67"/>
+      <c r="X39" s="68"/>
+      <c r="Y39" s="69"/>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C43" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="52"/>
+      <c r="E43" s="53"/>
+      <c r="G43" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="H26" s="28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C27" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="52"/>
-      <c r="E27" s="53"/>
-      <c r="G27" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-      <c r="K27" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="L27" s="52"/>
-      <c r="M27" s="53"/>
-      <c r="O27" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="53"/>
-      <c r="S27" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="T27" s="52"/>
-      <c r="U27" s="53"/>
-      <c r="W27" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="53"/>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C28" s="54"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="56"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="56"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="56"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="56"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="56"/>
-      <c r="W28" s="54"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="56"/>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C29" s="54"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="56"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="56"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="56"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="56"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="56"/>
-      <c r="W29" s="54"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="56"/>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C30" s="54"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="56"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="56"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="56"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="56"/>
-      <c r="S30" s="54"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="56"/>
-      <c r="W30" s="54"/>
-      <c r="X30" s="55"/>
-      <c r="Y30" s="56"/>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C31" s="54"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="56"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="56"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="56"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="56"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="56"/>
-      <c r="W31" s="54"/>
-      <c r="X31" s="55"/>
-      <c r="Y31" s="56"/>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C32" s="57"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="59"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="59"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="59"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="59"/>
-      <c r="S32" s="57"/>
-      <c r="T32" s="58"/>
-      <c r="U32" s="59"/>
-      <c r="W32" s="57"/>
-      <c r="X32" s="58"/>
-      <c r="Y32" s="59"/>
-    </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C34" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="53"/>
-      <c r="G34" s="51" t="s">
+      <c r="H43" s="52"/>
+      <c r="I43" s="53"/>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C44" s="57"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="56"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="56"/>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C45" s="57"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="56"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="77"/>
+      <c r="I45" s="56"/>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C46" s="57"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="56"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="56"/>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C47" s="57"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="56"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="56"/>
+    </row>
+    <row r="48" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="C48" s="58"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="60"/>
+    </row>
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C50" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="62"/>
+      <c r="E50" s="63"/>
+      <c r="G50" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="H34" s="52"/>
-      <c r="I34" s="53"/>
-      <c r="K34" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="L34" s="52"/>
-      <c r="M34" s="53"/>
-      <c r="O34" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="P34" s="52"/>
-      <c r="Q34" s="53"/>
-      <c r="S34" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="T34" s="52"/>
-      <c r="U34" s="53"/>
-      <c r="W34" s="51" t="s">
+      <c r="H50" s="62"/>
+      <c r="I50" s="63"/>
+      <c r="K50" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="X34" s="52"/>
-      <c r="Y34" s="53"/>
-    </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C35" s="54"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="56"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="56"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="56"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="55"/>
-      <c r="Q35" s="56"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="55"/>
-      <c r="U35" s="56"/>
-      <c r="W35" s="54"/>
-      <c r="X35" s="55"/>
-      <c r="Y35" s="56"/>
-    </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C36" s="54"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="56"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="O36" s="54"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="56"/>
-      <c r="S36" s="54"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="56"/>
-      <c r="W36" s="54"/>
-      <c r="X36" s="55"/>
-      <c r="Y36" s="56"/>
-    </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C37" s="54"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="56"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="56"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="56"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="55"/>
-      <c r="Y37" s="56"/>
-    </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C38" s="54"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="56"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="56"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="56"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="56"/>
-      <c r="S38" s="54"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="56"/>
-      <c r="W38" s="54"/>
-      <c r="X38" s="55"/>
-      <c r="Y38" s="56"/>
-    </row>
-    <row r="39" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C39" s="57"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="59"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="59"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="59"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="58"/>
-      <c r="Q39" s="59"/>
-      <c r="S39" s="57"/>
-      <c r="T39" s="58"/>
-      <c r="U39" s="59"/>
-      <c r="W39" s="57"/>
-      <c r="X39" s="58"/>
-      <c r="Y39" s="59"/>
-    </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C43" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="43"/>
-      <c r="E43" s="44"/>
-      <c r="G43" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="H43" s="43"/>
-      <c r="I43" s="44"/>
-    </row>
-    <row r="44" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C44" s="45"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="47"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="47"/>
-    </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C45" s="45"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="47"/>
-    </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C46" s="45"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="47"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="47"/>
-    </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C47" s="45"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="47"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="47"/>
-    </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C48" s="48"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="50"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="50"/>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C50" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="53"/>
-      <c r="G50" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H50" s="52"/>
-      <c r="I50" s="53"/>
-      <c r="K50" s="51" t="s">
+      <c r="L50" s="62"/>
+      <c r="M50" s="63"/>
+      <c r="O50" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="L50" s="52"/>
-      <c r="M50" s="53"/>
-      <c r="O50" s="51" t="s">
+      <c r="P50" s="62"/>
+      <c r="Q50" s="63"/>
+      <c r="S50" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="P50" s="52"/>
-      <c r="Q50" s="53"/>
-      <c r="S50" s="51" t="s">
+      <c r="T50" s="62"/>
+      <c r="U50" s="63"/>
+      <c r="W50" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="T50" s="52"/>
-      <c r="U50" s="53"/>
-      <c r="W50" s="51" t="s">
+      <c r="X50" s="62"/>
+      <c r="Y50" s="63"/>
+    </row>
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="66"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="66"/>
+      <c r="K51" s="64"/>
+      <c r="L51" s="65"/>
+      <c r="M51" s="66"/>
+      <c r="O51" s="64"/>
+      <c r="P51" s="65"/>
+      <c r="Q51" s="66"/>
+      <c r="S51" s="64"/>
+      <c r="T51" s="65"/>
+      <c r="U51" s="66"/>
+      <c r="W51" s="64"/>
+      <c r="X51" s="65"/>
+      <c r="Y51" s="66"/>
+    </row>
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="66"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="66"/>
+      <c r="K52" s="64"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="66"/>
+      <c r="O52" s="64"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="66"/>
+      <c r="S52" s="64"/>
+      <c r="T52" s="65"/>
+      <c r="U52" s="66"/>
+      <c r="W52" s="64"/>
+      <c r="X52" s="65"/>
+      <c r="Y52" s="66"/>
+    </row>
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C53" s="64"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="66"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="66"/>
+      <c r="K53" s="64"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="66"/>
+      <c r="O53" s="64"/>
+      <c r="P53" s="65"/>
+      <c r="Q53" s="66"/>
+      <c r="S53" s="64"/>
+      <c r="T53" s="65"/>
+      <c r="U53" s="66"/>
+      <c r="W53" s="64"/>
+      <c r="X53" s="65"/>
+      <c r="Y53" s="66"/>
+    </row>
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C54" s="64"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="66"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="66"/>
+      <c r="K54" s="64"/>
+      <c r="L54" s="65"/>
+      <c r="M54" s="66"/>
+      <c r="O54" s="64"/>
+      <c r="P54" s="65"/>
+      <c r="Q54" s="66"/>
+      <c r="S54" s="64"/>
+      <c r="T54" s="65"/>
+      <c r="U54" s="66"/>
+      <c r="W54" s="64"/>
+      <c r="X54" s="65"/>
+      <c r="Y54" s="66"/>
+    </row>
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="C55" s="67"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="69"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="69"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="68"/>
+      <c r="M55" s="69"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="68"/>
+      <c r="Q55" s="69"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="68"/>
+      <c r="U55" s="69"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="68"/>
+      <c r="Y55" s="69"/>
+    </row>
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B57" s="23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B58" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E58" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B60" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="53"/>
+    </row>
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B61" s="54"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="56"/>
+    </row>
+    <row r="62" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B62" s="54"/>
+      <c r="C62" s="55"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="56"/>
+    </row>
+    <row r="63" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B63" s="54"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="56"/>
+    </row>
+    <row r="64" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B64" s="54"/>
+      <c r="C64" s="55"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B65" s="54"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="56"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" s="54"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B67" s="54"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="55"/>
+      <c r="E67" s="55"/>
+      <c r="F67" s="55"/>
+      <c r="G67" s="56"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" s="57"/>
+      <c r="C68" s="55"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="56"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" s="57"/>
+      <c r="C69" s="55"/>
+      <c r="D69" s="55"/>
+      <c r="E69" s="55"/>
+      <c r="F69" s="55"/>
+      <c r="G69" s="56"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B70" s="57"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="55"/>
+      <c r="G70" s="56"/>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B71" s="58"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="60"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B73" s="23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A142" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="B142" s="23"/>
+      <c r="G142" s="23" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B145" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B146" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B147" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C148" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="D148" s="46"/>
+      <c r="E148" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="G148" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="H148" s="47"/>
+      <c r="I148" s="46"/>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A155" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="X50" s="52"/>
-      <c r="Y50" s="53"/>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C51" s="54"/>
-      <c r="D51" s="55"/>
-      <c r="E51" s="56"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="55"/>
-      <c r="I51" s="56"/>
-      <c r="K51" s="54"/>
-      <c r="L51" s="55"/>
-      <c r="M51" s="56"/>
-      <c r="O51" s="54"/>
-      <c r="P51" s="55"/>
-      <c r="Q51" s="56"/>
-      <c r="S51" s="54"/>
-      <c r="T51" s="55"/>
-      <c r="U51" s="56"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="55"/>
-      <c r="Y51" s="56"/>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C52" s="54"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="56"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="56"/>
-      <c r="K52" s="54"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="56"/>
-      <c r="O52" s="54"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="56"/>
-      <c r="S52" s="54"/>
-      <c r="T52" s="55"/>
-      <c r="U52" s="56"/>
-      <c r="W52" s="54"/>
-      <c r="X52" s="55"/>
-      <c r="Y52" s="56"/>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C53" s="54"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="56"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="55"/>
-      <c r="I53" s="56"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="55"/>
-      <c r="M53" s="56"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="55"/>
-      <c r="Q53" s="56"/>
-      <c r="S53" s="54"/>
-      <c r="T53" s="55"/>
-      <c r="U53" s="56"/>
-      <c r="W53" s="54"/>
-      <c r="X53" s="55"/>
-      <c r="Y53" s="56"/>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C54" s="54"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="56"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="56"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="55"/>
-      <c r="M54" s="56"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="55"/>
-      <c r="Q54" s="56"/>
-      <c r="S54" s="54"/>
-      <c r="T54" s="55"/>
-      <c r="U54" s="56"/>
-      <c r="W54" s="54"/>
-      <c r="X54" s="55"/>
-      <c r="Y54" s="56"/>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C55" s="57"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="59"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="59"/>
-      <c r="K55" s="57"/>
-      <c r="L55" s="58"/>
-      <c r="M55" s="59"/>
-      <c r="O55" s="57"/>
-      <c r="P55" s="58"/>
-      <c r="Q55" s="59"/>
-      <c r="S55" s="57"/>
-      <c r="T55" s="58"/>
-      <c r="U55" s="59"/>
-      <c r="W55" s="57"/>
-      <c r="X55" s="58"/>
-      <c r="Y55" s="59"/>
-    </row>
-    <row r="67" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A67" s="29" t="s">
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B156" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="79"/>
+      <c r="D156" s="80"/>
+      <c r="F156" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G156" s="52"/>
+      <c r="H156" s="53"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B157" s="81"/>
+      <c r="C157" s="82"/>
+      <c r="D157" s="83"/>
+      <c r="F157" s="57"/>
+      <c r="G157" s="77"/>
+      <c r="H157" s="56"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B158" s="81"/>
+      <c r="C158" s="82"/>
+      <c r="D158" s="83"/>
+      <c r="E158" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F158" s="57"/>
+      <c r="G158" s="77"/>
+      <c r="H158" s="56"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B159" s="81"/>
+      <c r="C159" s="82"/>
+      <c r="D159" s="83"/>
+      <c r="F159" s="57"/>
+      <c r="G159" s="77"/>
+      <c r="H159" s="56"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B160" s="81"/>
+      <c r="C160" s="82"/>
+      <c r="D160" s="83"/>
+      <c r="F160" s="57"/>
+      <c r="G160" s="77"/>
+      <c r="H160" s="56"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B161" s="84"/>
+      <c r="C161" s="85"/>
+      <c r="D161" s="86"/>
+      <c r="F161" s="58"/>
+      <c r="G161" s="59"/>
+      <c r="H161" s="60"/>
+    </row>
+    <row r="163" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A163" s="29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B164" s="51"/>
+      <c r="C164" s="52"/>
+      <c r="D164" s="53"/>
+      <c r="F164" s="51" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="61"/>
-      <c r="D68" s="62"/>
-      <c r="F68" s="42" t="s">
+      <c r="G164" s="52"/>
+      <c r="H164" s="53"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B165" s="57"/>
+      <c r="C165" s="77"/>
+      <c r="D165" s="56"/>
+      <c r="F165" s="57"/>
+      <c r="G165" s="77"/>
+      <c r="H165" s="56"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B166" s="57"/>
+      <c r="C166" s="77"/>
+      <c r="D166" s="56"/>
+      <c r="F166" s="57"/>
+      <c r="G166" s="77"/>
+      <c r="H166" s="56"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B167" s="57"/>
+      <c r="C167" s="77"/>
+      <c r="D167" s="56"/>
+      <c r="F167" s="57"/>
+      <c r="G167" s="77"/>
+      <c r="H167" s="56"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B168" s="57"/>
+      <c r="C168" s="77"/>
+      <c r="D168" s="56"/>
+      <c r="F168" s="57"/>
+      <c r="G168" s="77"/>
+      <c r="H168" s="56"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B169" s="58"/>
+      <c r="C169" s="59"/>
+      <c r="D169" s="60"/>
+      <c r="F169" s="58"/>
+      <c r="G169" s="59"/>
+      <c r="H169" s="60"/>
+    </row>
+    <row r="173" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A173" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D173" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B174" t="s">
+        <v>92</v>
+      </c>
+      <c r="F174" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B175" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C175" s="52"/>
+      <c r="D175" s="53"/>
+      <c r="F175" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="G175" s="52"/>
+      <c r="H175" s="53"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B176" s="57"/>
+      <c r="C176" s="77"/>
+      <c r="D176" s="56"/>
+      <c r="F176" s="57"/>
+      <c r="G176" s="77"/>
+      <c r="H176" s="56"/>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B177" s="57"/>
+      <c r="C177" s="77"/>
+      <c r="D177" s="56"/>
+      <c r="F177" s="57"/>
+      <c r="G177" s="77"/>
+      <c r="H177" s="56"/>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B178" s="57"/>
+      <c r="C178" s="77"/>
+      <c r="D178" s="56"/>
+      <c r="E178" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="G68" s="43"/>
-      <c r="H68" s="44"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="63"/>
-      <c r="C69" s="64"/>
-      <c r="D69" s="65"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="47"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B70" s="63"/>
-      <c r="C70" s="64"/>
-      <c r="D70" s="65"/>
-      <c r="E70" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F70" s="45"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="47"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B71" s="63"/>
-      <c r="C71" s="64"/>
-      <c r="D71" s="65"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="47"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B72" s="63"/>
-      <c r="C72" s="64"/>
-      <c r="D72" s="65"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="47"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B73" s="66"/>
-      <c r="C73" s="67"/>
-      <c r="D73" s="68"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="50"/>
-    </row>
-    <row r="75" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B76" s="42"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="44"/>
-      <c r="F76" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="G76" s="43"/>
-      <c r="H76" s="44"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B77" s="45"/>
-      <c r="C77" s="46"/>
-      <c r="D77" s="47"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="47"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B78" s="45"/>
-      <c r="C78" s="46"/>
-      <c r="D78" s="47"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="47"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="45"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="47"/>
-      <c r="F79" s="45"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="47"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="45"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="47"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="47"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="48"/>
-      <c r="C81" s="49"/>
-      <c r="D81" s="50"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="50"/>
-    </row>
-    <row r="85" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A85" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B86" t="s">
-        <v>93</v>
-      </c>
-      <c r="F86" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C87" s="43"/>
-      <c r="D87" s="44"/>
-      <c r="F87" s="42" t="s">
+      <c r="F178" s="57"/>
+      <c r="G178" s="77"/>
+      <c r="H178" s="56"/>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B179" s="57"/>
+      <c r="C179" s="77"/>
+      <c r="D179" s="56"/>
+      <c r="F179" s="57"/>
+      <c r="G179" s="77"/>
+      <c r="H179" s="56"/>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B180" s="57"/>
+      <c r="C180" s="77"/>
+      <c r="D180" s="56"/>
+      <c r="F180" s="57"/>
+      <c r="G180" s="77"/>
+      <c r="H180" s="56"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B181" s="57"/>
+      <c r="C181" s="77"/>
+      <c r="D181" s="56"/>
+      <c r="F181" s="57"/>
+      <c r="G181" s="77"/>
+      <c r="H181" s="56"/>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B182" s="58"/>
+      <c r="C182" s="59"/>
+      <c r="D182" s="60"/>
+      <c r="F182" s="58"/>
+      <c r="G182" s="59"/>
+      <c r="H182" s="60"/>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B183" t="s">
         <v>95</v>
       </c>
-      <c r="G87" s="43"/>
-      <c r="H87" s="44"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B88" s="45"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="47"/>
-      <c r="F88" s="45"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="47"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B89" s="45"/>
-      <c r="C89" s="46"/>
-      <c r="D89" s="47"/>
-      <c r="F89" s="45"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="47"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B90" s="45"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="47"/>
-      <c r="E90" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F90" s="45"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="47"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B91" s="45"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="47"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="47"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B92" s="45"/>
-      <c r="C92" s="46"/>
-      <c r="D92" s="47"/>
-      <c r="F92" s="45"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="47"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B93" s="45"/>
-      <c r="C93" s="46"/>
-      <c r="D93" s="47"/>
-      <c r="F93" s="45"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="47"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B94" s="48"/>
-      <c r="C94" s="49"/>
-      <c r="D94" s="50"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="49"/>
-      <c r="H94" s="50"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B95" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A98" s="29" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="81" t="s">
+    </row>
+    <row r="186" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A186" s="29" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B187" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="F187" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="F99" s="81" t="s">
+      <c r="J187" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B189" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C189" s="62"/>
+      <c r="D189" s="63"/>
+      <c r="F189" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="G189" s="62"/>
+      <c r="H189" s="63"/>
+      <c r="J189" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="K189" s="52"/>
+      <c r="L189" s="53"/>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B190" s="67"/>
+      <c r="C190" s="68"/>
+      <c r="D190" s="69"/>
+      <c r="F190" s="67"/>
+      <c r="G190" s="68"/>
+      <c r="H190" s="69"/>
+      <c r="J190" s="57"/>
+      <c r="K190" s="77"/>
+      <c r="L190" s="56"/>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B191" s="27"/>
+      <c r="C191" s="27"/>
+      <c r="D191" s="27"/>
+      <c r="F191" s="27"/>
+      <c r="G191" s="27"/>
+      <c r="H191" s="27"/>
+      <c r="J191" s="57"/>
+      <c r="K191" s="77"/>
+      <c r="L191" s="56"/>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B192" t="s">
+        <v>203</v>
+      </c>
+      <c r="F192" t="s">
+        <v>203</v>
+      </c>
+      <c r="J192" s="57"/>
+      <c r="K192" s="77"/>
+      <c r="L192" s="56"/>
+    </row>
+    <row r="193" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B193" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="J99" t="s">
+      <c r="C193" s="52"/>
+      <c r="D193" s="53"/>
+      <c r="F193" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="G193" s="52"/>
+      <c r="H193" s="53"/>
+      <c r="J193" s="57"/>
+      <c r="K193" s="77"/>
+      <c r="L193" s="56"/>
+    </row>
+    <row r="194" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B194" s="57"/>
+      <c r="C194" s="77"/>
+      <c r="D194" s="56"/>
+      <c r="F194" s="57"/>
+      <c r="G194" s="77"/>
+      <c r="H194" s="56"/>
+      <c r="J194" s="57"/>
+      <c r="K194" s="77"/>
+      <c r="L194" s="56"/>
+    </row>
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B195" s="57"/>
+      <c r="C195" s="77"/>
+      <c r="D195" s="56"/>
+      <c r="F195" s="57"/>
+      <c r="G195" s="77"/>
+      <c r="H195" s="56"/>
+      <c r="J195" s="57"/>
+      <c r="K195" s="77"/>
+      <c r="L195" s="56"/>
+    </row>
+    <row r="196" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B196" s="57"/>
+      <c r="C196" s="77"/>
+      <c r="D196" s="56"/>
+      <c r="F196" s="57"/>
+      <c r="G196" s="77"/>
+      <c r="H196" s="56"/>
+      <c r="J196" s="57"/>
+      <c r="K196" s="77"/>
+      <c r="L196" s="56"/>
+    </row>
+    <row r="197" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B197" s="57"/>
+      <c r="C197" s="77"/>
+      <c r="D197" s="56"/>
+      <c r="F197" s="57"/>
+      <c r="G197" s="77"/>
+      <c r="H197" s="56"/>
+      <c r="J197" s="57"/>
+      <c r="K197" s="77"/>
+      <c r="L197" s="56"/>
+    </row>
+    <row r="198" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B198" s="57"/>
+      <c r="C198" s="77"/>
+      <c r="D198" s="56"/>
+      <c r="F198" s="57"/>
+      <c r="G198" s="77"/>
+      <c r="H198" s="56"/>
+      <c r="J198" s="58"/>
+      <c r="K198" s="59"/>
+      <c r="L198" s="60"/>
+    </row>
+    <row r="199" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B199" s="57"/>
+      <c r="C199" s="77"/>
+      <c r="D199" s="56"/>
+      <c r="E199" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F199" s="57"/>
+      <c r="G199" s="77"/>
+      <c r="H199" s="56"/>
+    </row>
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B200" s="57"/>
+      <c r="C200" s="77"/>
+      <c r="D200" s="56"/>
+      <c r="F200" s="57"/>
+      <c r="G200" s="77"/>
+      <c r="H200" s="56"/>
+      <c r="J200" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B100" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B101" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="C101" s="52"/>
-      <c r="D101" s="53"/>
-      <c r="F101" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="G101" s="52"/>
-      <c r="H101" s="53"/>
-      <c r="J101" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="K101" s="43"/>
-      <c r="L101" s="44"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B102" s="57"/>
-      <c r="C102" s="58"/>
-      <c r="D102" s="59"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="58"/>
-      <c r="H102" s="59"/>
-      <c r="J102" s="45"/>
-      <c r="K102" s="46"/>
-      <c r="L102" s="47"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
-      <c r="D103" s="27"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="27"/>
-      <c r="J103" s="45"/>
-      <c r="K103" s="46"/>
-      <c r="L103" s="47"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B104" t="s">
-        <v>204</v>
-      </c>
-      <c r="F104" t="s">
-        <v>204</v>
-      </c>
-      <c r="J104" s="45"/>
-      <c r="K104" s="46"/>
-      <c r="L104" s="47"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B105" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
-      <c r="F105" s="42" t="s">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B201" s="57"/>
+      <c r="C201" s="77"/>
+      <c r="D201" s="56"/>
+      <c r="F201" s="57"/>
+      <c r="G201" s="77"/>
+      <c r="H201" s="56"/>
+      <c r="K201" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="202" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B202" s="57"/>
+      <c r="C202" s="77"/>
+      <c r="D202" s="56"/>
+      <c r="F202" s="57"/>
+      <c r="G202" s="77"/>
+      <c r="H202" s="56"/>
+    </row>
+    <row r="203" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B203" s="57"/>
+      <c r="C203" s="77"/>
+      <c r="D203" s="56"/>
+      <c r="F203" s="57"/>
+      <c r="G203" s="77"/>
+      <c r="H203" s="56"/>
+    </row>
+    <row r="204" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B204" s="57"/>
+      <c r="C204" s="77"/>
+      <c r="D204" s="56"/>
+      <c r="F204" s="57"/>
+      <c r="G204" s="77"/>
+      <c r="H204" s="56"/>
+    </row>
+    <row r="205" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B205" s="57"/>
+      <c r="C205" s="77"/>
+      <c r="D205" s="56"/>
+      <c r="F205" s="57"/>
+      <c r="G205" s="77"/>
+      <c r="H205" s="56"/>
+    </row>
+    <row r="206" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B206" s="58"/>
+      <c r="C206" s="59"/>
+      <c r="D206" s="60"/>
+      <c r="F206" s="58"/>
+      <c r="G206" s="59"/>
+      <c r="H206" s="60"/>
+    </row>
+    <row r="208" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B208" t="s">
+        <v>199</v>
+      </c>
+      <c r="F208" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B209" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="C209" s="52"/>
+      <c r="D209" s="53"/>
+      <c r="F209" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="G105" s="43"/>
-      <c r="H105" s="44"/>
-      <c r="J105" s="45"/>
-      <c r="K105" s="46"/>
-      <c r="L105" s="47"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B106" s="45"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="47"/>
-      <c r="F106" s="45"/>
-      <c r="G106" s="46"/>
-      <c r="H106" s="47"/>
-      <c r="J106" s="45"/>
-      <c r="K106" s="46"/>
-      <c r="L106" s="47"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B107" s="45"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="47"/>
-      <c r="F107" s="45"/>
-      <c r="G107" s="46"/>
-      <c r="H107" s="47"/>
-      <c r="J107" s="45"/>
-      <c r="K107" s="46"/>
-      <c r="L107" s="47"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B108" s="45"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="47"/>
-      <c r="F108" s="45"/>
-      <c r="G108" s="46"/>
-      <c r="H108" s="47"/>
-      <c r="J108" s="45"/>
-      <c r="K108" s="46"/>
-      <c r="L108" s="47"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B109" s="45"/>
-      <c r="C109" s="46"/>
-      <c r="D109" s="47"/>
-      <c r="F109" s="45"/>
-      <c r="G109" s="46"/>
-      <c r="H109" s="47"/>
-      <c r="J109" s="45"/>
-      <c r="K109" s="46"/>
-      <c r="L109" s="47"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B110" s="45"/>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47"/>
-      <c r="F110" s="45"/>
-      <c r="G110" s="46"/>
-      <c r="H110" s="47"/>
-      <c r="J110" s="48"/>
-      <c r="K110" s="49"/>
-      <c r="L110" s="50"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B111" s="45"/>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F111" s="45"/>
-      <c r="G111" s="46"/>
-      <c r="H111" s="47"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B112" s="45"/>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47"/>
-      <c r="F112" s="45"/>
-      <c r="G112" s="46"/>
-      <c r="H112" s="47"/>
-      <c r="J112" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B113" s="45"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="47"/>
-      <c r="F113" s="45"/>
-      <c r="G113" s="46"/>
-      <c r="H113" s="47"/>
-      <c r="K113" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B114" s="45"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="47"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="46"/>
-      <c r="H114" s="47"/>
-    </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B115" s="45"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="47"/>
-      <c r="F115" s="45"/>
-      <c r="G115" s="46"/>
-      <c r="H115" s="47"/>
-    </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B116" s="45"/>
-      <c r="C116" s="46"/>
-      <c r="D116" s="47"/>
-      <c r="F116" s="45"/>
-      <c r="G116" s="46"/>
-      <c r="H116" s="47"/>
-    </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B117" s="45"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="47"/>
-      <c r="F117" s="45"/>
-      <c r="G117" s="46"/>
-      <c r="H117" s="47"/>
-    </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B118" s="48"/>
-      <c r="C118" s="49"/>
-      <c r="D118" s="50"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="49"/>
-      <c r="H118" s="50"/>
-    </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B120" t="s">
+      <c r="G209" s="52"/>
+      <c r="H209" s="53"/>
+      <c r="J209" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="F120" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B121" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="C121" s="43"/>
-      <c r="D121" s="44"/>
-      <c r="F121" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="G121" s="43"/>
-      <c r="H121" s="44"/>
-      <c r="J121" s="42" t="s">
+      <c r="K209" s="52"/>
+      <c r="L209" s="53"/>
+    </row>
+    <row r="210" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B210" s="57"/>
+      <c r="C210" s="77"/>
+      <c r="D210" s="56"/>
+      <c r="F210" s="57"/>
+      <c r="G210" s="77"/>
+      <c r="H210" s="56"/>
+      <c r="J210" s="57"/>
+      <c r="K210" s="77"/>
+      <c r="L210" s="56"/>
+    </row>
+    <row r="211" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B211" s="57"/>
+      <c r="C211" s="77"/>
+      <c r="D211" s="56"/>
+      <c r="F211" s="57"/>
+      <c r="G211" s="77"/>
+      <c r="H211" s="56"/>
+      <c r="J211" s="57"/>
+      <c r="K211" s="77"/>
+      <c r="L211" s="56"/>
+    </row>
+    <row r="212" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B212" s="57"/>
+      <c r="C212" s="77"/>
+      <c r="D212" s="56"/>
+      <c r="F212" s="57"/>
+      <c r="G212" s="77"/>
+      <c r="H212" s="56"/>
+      <c r="J212" s="57"/>
+      <c r="K212" s="77"/>
+      <c r="L212" s="56"/>
+    </row>
+    <row r="213" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B213" s="57"/>
+      <c r="C213" s="77"/>
+      <c r="D213" s="56"/>
+      <c r="F213" s="57"/>
+      <c r="G213" s="77"/>
+      <c r="H213" s="56"/>
+      <c r="J213" s="57"/>
+      <c r="K213" s="77"/>
+      <c r="L213" s="56"/>
+    </row>
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B214" s="57"/>
+      <c r="C214" s="77"/>
+      <c r="D214" s="56"/>
+      <c r="F214" s="57"/>
+      <c r="G214" s="77"/>
+      <c r="H214" s="56"/>
+      <c r="J214" s="57"/>
+      <c r="K214" s="77"/>
+      <c r="L214" s="56"/>
+    </row>
+    <row r="215" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B215" s="57"/>
+      <c r="C215" s="77"/>
+      <c r="D215" s="56"/>
+      <c r="E215" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F215" s="57"/>
+      <c r="G215" s="77"/>
+      <c r="H215" s="56"/>
+      <c r="J215" s="57"/>
+      <c r="K215" s="77"/>
+      <c r="L215" s="56"/>
+    </row>
+    <row r="216" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B216" s="57"/>
+      <c r="C216" s="77"/>
+      <c r="D216" s="56"/>
+      <c r="F216" s="57"/>
+      <c r="G216" s="77"/>
+      <c r="H216" s="56"/>
+      <c r="J216" s="57"/>
+      <c r="K216" s="77"/>
+      <c r="L216" s="56"/>
+    </row>
+    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B217" s="57"/>
+      <c r="C217" s="77"/>
+      <c r="D217" s="56"/>
+      <c r="F217" s="57"/>
+      <c r="G217" s="77"/>
+      <c r="H217" s="56"/>
+      <c r="J217" s="58"/>
+      <c r="K217" s="59"/>
+      <c r="L217" s="60"/>
+    </row>
+    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B218" s="57"/>
+      <c r="C218" s="77"/>
+      <c r="D218" s="56"/>
+      <c r="F218" s="57"/>
+      <c r="G218" s="77"/>
+      <c r="H218" s="56"/>
+    </row>
+    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B219" s="57"/>
+      <c r="C219" s="77"/>
+      <c r="D219" s="56"/>
+      <c r="F219" s="57"/>
+      <c r="G219" s="77"/>
+      <c r="H219" s="56"/>
+      <c r="J219" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B220" s="57"/>
+      <c r="C220" s="77"/>
+      <c r="D220" s="56"/>
+      <c r="F220" s="57"/>
+      <c r="G220" s="77"/>
+      <c r="H220" s="56"/>
+      <c r="K220" t="s">
         <v>201</v>
       </c>
-      <c r="K121" s="43"/>
-      <c r="L121" s="44"/>
-    </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B122" s="45"/>
-      <c r="C122" s="46"/>
-      <c r="D122" s="47"/>
-      <c r="F122" s="45"/>
-      <c r="G122" s="46"/>
-      <c r="H122" s="47"/>
-      <c r="J122" s="45"/>
-      <c r="K122" s="46"/>
-      <c r="L122" s="47"/>
-    </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B123" s="45"/>
-      <c r="C123" s="46"/>
-      <c r="D123" s="47"/>
-      <c r="F123" s="45"/>
-      <c r="G123" s="46"/>
-      <c r="H123" s="47"/>
-      <c r="J123" s="45"/>
-      <c r="K123" s="46"/>
-      <c r="L123" s="47"/>
-    </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B124" s="45"/>
-      <c r="C124" s="46"/>
-      <c r="D124" s="47"/>
-      <c r="F124" s="45"/>
-      <c r="G124" s="46"/>
-      <c r="H124" s="47"/>
-      <c r="J124" s="45"/>
-      <c r="K124" s="46"/>
-      <c r="L124" s="47"/>
-    </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B125" s="45"/>
-      <c r="C125" s="46"/>
-      <c r="D125" s="47"/>
-      <c r="F125" s="45"/>
-      <c r="G125" s="46"/>
-      <c r="H125" s="47"/>
-      <c r="J125" s="45"/>
-      <c r="K125" s="46"/>
-      <c r="L125" s="47"/>
-    </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B126" s="45"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="47"/>
-      <c r="F126" s="45"/>
-      <c r="G126" s="46"/>
-      <c r="H126" s="47"/>
-      <c r="J126" s="45"/>
-      <c r="K126" s="46"/>
-      <c r="L126" s="47"/>
-    </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B127" s="45"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="47"/>
-      <c r="E127" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F127" s="45"/>
-      <c r="G127" s="46"/>
-      <c r="H127" s="47"/>
-      <c r="J127" s="45"/>
-      <c r="K127" s="46"/>
-      <c r="L127" s="47"/>
-    </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B128" s="45"/>
-      <c r="C128" s="46"/>
-      <c r="D128" s="47"/>
-      <c r="F128" s="45"/>
-      <c r="G128" s="46"/>
-      <c r="H128" s="47"/>
-      <c r="J128" s="45"/>
-      <c r="K128" s="46"/>
-      <c r="L128" s="47"/>
-    </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B129" s="45"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="47"/>
-      <c r="F129" s="45"/>
-      <c r="G129" s="46"/>
-      <c r="H129" s="47"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="50"/>
-    </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B130" s="45"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="47"/>
-      <c r="F130" s="45"/>
-      <c r="G130" s="46"/>
-      <c r="H130" s="47"/>
-    </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B131" s="45"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="47"/>
-      <c r="F131" s="45"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="47"/>
-      <c r="J131" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B132" s="45"/>
-      <c r="C132" s="46"/>
-      <c r="D132" s="47"/>
-      <c r="F132" s="45"/>
-      <c r="G132" s="46"/>
-      <c r="H132" s="47"/>
-      <c r="K132" t="s">
+    </row>
+    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B221" s="57"/>
+      <c r="C221" s="77"/>
+      <c r="D221" s="56"/>
+      <c r="F221" s="57"/>
+      <c r="G221" s="77"/>
+      <c r="H221" s="56"/>
+      <c r="K221" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B133" s="45"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="47"/>
-      <c r="F133" s="45"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="47"/>
-      <c r="K133" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B134" s="48"/>
-      <c r="C134" s="49"/>
-      <c r="D134" s="50"/>
-      <c r="F134" s="48"/>
-      <c r="G134" s="49"/>
-      <c r="H134" s="50"/>
+    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B222" s="58"/>
+      <c r="C222" s="59"/>
+      <c r="D222" s="60"/>
+      <c r="F222" s="58"/>
+      <c r="G222" s="59"/>
+      <c r="H222" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B121:D134"/>
-    <mergeCell ref="F121:H134"/>
-    <mergeCell ref="J121:L129"/>
+  <mergeCells count="36">
+    <mergeCell ref="B209:D222"/>
+    <mergeCell ref="F209:H222"/>
+    <mergeCell ref="J209:L217"/>
     <mergeCell ref="S50:U55"/>
     <mergeCell ref="W50:Y55"/>
-    <mergeCell ref="B105:D118"/>
-    <mergeCell ref="F105:H118"/>
-    <mergeCell ref="B101:D102"/>
-    <mergeCell ref="F101:H102"/>
-    <mergeCell ref="J101:L110"/>
+    <mergeCell ref="B193:D206"/>
+    <mergeCell ref="F193:H206"/>
+    <mergeCell ref="B189:D190"/>
+    <mergeCell ref="F189:H190"/>
+    <mergeCell ref="J189:L198"/>
+    <mergeCell ref="B175:D182"/>
+    <mergeCell ref="F175:H182"/>
+    <mergeCell ref="B164:D169"/>
+    <mergeCell ref="B156:D161"/>
+    <mergeCell ref="F164:H169"/>
+    <mergeCell ref="F156:H161"/>
     <mergeCell ref="C4:H7"/>
     <mergeCell ref="C34:E39"/>
     <mergeCell ref="G50:I55"/>
@@ -4970,72 +8460,68 @@
     <mergeCell ref="G34:I39"/>
     <mergeCell ref="C27:E32"/>
     <mergeCell ref="G27:I32"/>
-    <mergeCell ref="B87:D94"/>
-    <mergeCell ref="F87:H94"/>
-    <mergeCell ref="S34:U39"/>
-    <mergeCell ref="W34:Y39"/>
     <mergeCell ref="K27:M32"/>
     <mergeCell ref="O27:Q32"/>
     <mergeCell ref="S27:U32"/>
     <mergeCell ref="W27:Y32"/>
-    <mergeCell ref="B76:D81"/>
     <mergeCell ref="K34:M39"/>
     <mergeCell ref="O34:Q39"/>
-    <mergeCell ref="B68:D73"/>
-    <mergeCell ref="F76:H81"/>
-    <mergeCell ref="F68:H73"/>
+    <mergeCell ref="B60:G71"/>
     <mergeCell ref="K50:M55"/>
     <mergeCell ref="O50:Q55"/>
+    <mergeCell ref="S34:U39"/>
+    <mergeCell ref="W34:Y39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84513203-8B75-439A-83DC-F0433279F24C}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.5">
       <c r="A1" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B2" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B3" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="B4" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B5" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B7" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
@@ -5043,17 +8529,17 @@
     </row>
     <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B10" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B11" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B12" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
@@ -5061,114 +8547,114 @@
     </row>
     <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B14" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="B18" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="B26" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="24" x14ac:dyDescent="0.2">
       <c r="B35" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
     </row>
     <row r="37" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B37" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="36" t="s">
         <v>149</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>150</v>
       </c>
       <c r="H37" s="36" t="s">
         <v>8</v>
@@ -5176,70 +8662,731 @@
     </row>
     <row r="38" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B38" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="H38" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B39" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="H39" s="39" t="s">
         <v>155</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B40" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="H40" s="40" t="s">
         <v>158</v>
-      </c>
-      <c r="H40" s="40" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="24" x14ac:dyDescent="0.2">
       <c r="B42" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B43" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B44" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B45" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B46" s="33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="A50" s="88" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="B52" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B53" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B54" s="89" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B55" s="93" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C56" s="91" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B57" s="92" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B58" s="92" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C59" s="107" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="98"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="98"/>
+      <c r="G59" s="98"/>
+      <c r="H59" s="98"/>
+      <c r="I59" s="99"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C60" s="103" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="102"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C61" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="101"/>
+      <c r="E61" s="101"/>
+      <c r="F61" s="101"/>
+      <c r="G61" s="101"/>
+      <c r="H61" s="101"/>
+      <c r="I61" s="102"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C62" s="108"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="101"/>
+      <c r="I62" s="102"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C63" s="109" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" s="101"/>
+      <c r="E63" s="101"/>
+      <c r="F63" s="101"/>
+      <c r="G63" s="101"/>
+      <c r="H63" s="101"/>
+      <c r="I63" s="102"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C64" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="D64" s="101"/>
+      <c r="E64" s="101"/>
+      <c r="F64" s="101"/>
+      <c r="G64" s="101"/>
+      <c r="H64" s="101"/>
+      <c r="I64" s="102"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C65" s="108"/>
+      <c r="D65" s="101"/>
+      <c r="E65" s="101"/>
+      <c r="F65" s="101"/>
+      <c r="G65" s="101"/>
+      <c r="H65" s="101"/>
+      <c r="I65" s="102"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C66" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="102"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C67" s="109" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" s="101"/>
+      <c r="E67" s="101"/>
+      <c r="F67" s="101"/>
+      <c r="G67" s="101"/>
+      <c r="H67" s="101"/>
+      <c r="I67" s="102"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C68" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="D68" s="101"/>
+      <c r="E68" s="101"/>
+      <c r="F68" s="101"/>
+      <c r="G68" s="101"/>
+      <c r="H68" s="101"/>
+      <c r="I68" s="102"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C69" s="108"/>
+      <c r="D69" s="101"/>
+      <c r="E69" s="101"/>
+      <c r="F69" s="101"/>
+      <c r="G69" s="101"/>
+      <c r="H69" s="101"/>
+      <c r="I69" s="102"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C70" s="109" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" s="101"/>
+      <c r="E70" s="101"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="102"/>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C71" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="D71" s="101"/>
+      <c r="E71" s="101"/>
+      <c r="F71" s="101"/>
+      <c r="G71" s="101"/>
+      <c r="H71" s="101"/>
+      <c r="I71" s="102"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C72" s="108"/>
+      <c r="D72" s="101"/>
+      <c r="E72" s="101"/>
+      <c r="F72" s="101"/>
+      <c r="G72" s="101"/>
+      <c r="H72" s="101"/>
+      <c r="I72" s="102"/>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C73" s="109" t="s">
+        <v>246</v>
+      </c>
+      <c r="D73" s="101"/>
+      <c r="E73" s="101"/>
+      <c r="F73" s="101"/>
+      <c r="G73" s="101"/>
+      <c r="H73" s="101"/>
+      <c r="I73" s="102"/>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C74" s="110" t="s">
+        <v>247</v>
+      </c>
+      <c r="D74" s="105"/>
+      <c r="E74" s="105"/>
+      <c r="F74" s="105"/>
+      <c r="G74" s="105"/>
+      <c r="H74" s="105"/>
+      <c r="I74" s="106"/>
+    </row>
+    <row r="75" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B75" s="95" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B76" s="87" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C77" s="97" t="s">
+        <v>250</v>
+      </c>
+      <c r="D77" s="98"/>
+      <c r="E77" s="98"/>
+      <c r="F77" s="98"/>
+      <c r="G77" s="98"/>
+      <c r="H77" s="98"/>
+      <c r="I77" s="98"/>
+      <c r="J77" s="98"/>
+      <c r="K77" s="99"/>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C78" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="D78" s="101"/>
+      <c r="E78" s="101"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="101"/>
+      <c r="K78" s="102"/>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C79" s="100" t="s">
+        <v>252</v>
+      </c>
+      <c r="D79" s="101"/>
+      <c r="E79" s="101"/>
+      <c r="F79" s="101"/>
+      <c r="G79" s="101"/>
+      <c r="H79" s="101"/>
+      <c r="I79" s="101"/>
+      <c r="J79" s="101"/>
+      <c r="K79" s="102"/>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C80" s="100" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80" s="101"/>
+      <c r="E80" s="101"/>
+      <c r="F80" s="101"/>
+      <c r="G80" s="101"/>
+      <c r="H80" s="101"/>
+      <c r="I80" s="101"/>
+      <c r="J80" s="101"/>
+      <c r="K80" s="102"/>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C81" s="100" t="s">
+        <v>254</v>
+      </c>
+      <c r="D81" s="101"/>
+      <c r="E81" s="101"/>
+      <c r="F81" s="101"/>
+      <c r="G81" s="101"/>
+      <c r="H81" s="101"/>
+      <c r="I81" s="101"/>
+      <c r="J81" s="101"/>
+      <c r="K81" s="102"/>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C82" s="100" t="s">
+        <v>255</v>
+      </c>
+      <c r="D82" s="101"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="101"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="101"/>
+      <c r="I82" s="101"/>
+      <c r="J82" s="101"/>
+      <c r="K82" s="102"/>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C83" s="100" t="s">
+        <v>256</v>
+      </c>
+      <c r="D83" s="101"/>
+      <c r="E83" s="101"/>
+      <c r="F83" s="101"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="101"/>
+      <c r="I83" s="101"/>
+      <c r="J83" s="101"/>
+      <c r="K83" s="102"/>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C84" s="103" t="s">
+        <v>257</v>
+      </c>
+      <c r="D84" s="101"/>
+      <c r="E84" s="101"/>
+      <c r="F84" s="101"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="101"/>
+      <c r="I84" s="101"/>
+      <c r="J84" s="101"/>
+      <c r="K84" s="102"/>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C85" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="D85" s="101"/>
+      <c r="E85" s="101"/>
+      <c r="F85" s="101"/>
+      <c r="G85" s="101"/>
+      <c r="H85" s="101"/>
+      <c r="I85" s="101"/>
+      <c r="J85" s="101"/>
+      <c r="K85" s="102"/>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C86" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="D86" s="101"/>
+      <c r="E86" s="101"/>
+      <c r="F86" s="101"/>
+      <c r="G86" s="101"/>
+      <c r="H86" s="101"/>
+      <c r="I86" s="101"/>
+      <c r="J86" s="101"/>
+      <c r="K86" s="102"/>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C87" s="100" t="s">
+        <v>260</v>
+      </c>
+      <c r="D87" s="101"/>
+      <c r="E87" s="101"/>
+      <c r="F87" s="101"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="101"/>
+      <c r="I87" s="101"/>
+      <c r="J87" s="101"/>
+      <c r="K87" s="102"/>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C88" s="100" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" s="101"/>
+      <c r="E88" s="101"/>
+      <c r="F88" s="101"/>
+      <c r="G88" s="101"/>
+      <c r="H88" s="101"/>
+      <c r="I88" s="101"/>
+      <c r="J88" s="101"/>
+      <c r="K88" s="102"/>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C89" s="103" t="s">
+        <v>262</v>
+      </c>
+      <c r="D89" s="101"/>
+      <c r="E89" s="101"/>
+      <c r="F89" s="101"/>
+      <c r="G89" s="101"/>
+      <c r="H89" s="101"/>
+      <c r="I89" s="101"/>
+      <c r="J89" s="101"/>
+      <c r="K89" s="102"/>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C90" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="D90" s="101"/>
+      <c r="E90" s="101"/>
+      <c r="F90" s="101"/>
+      <c r="G90" s="101"/>
+      <c r="H90" s="101"/>
+      <c r="I90" s="101"/>
+      <c r="J90" s="101"/>
+      <c r="K90" s="102"/>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C91" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="D91" s="101"/>
+      <c r="E91" s="101"/>
+      <c r="F91" s="101"/>
+      <c r="G91" s="101"/>
+      <c r="H91" s="101"/>
+      <c r="I91" s="101"/>
+      <c r="J91" s="101"/>
+      <c r="K91" s="102"/>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C92" s="104" t="s">
+        <v>265</v>
+      </c>
+      <c r="D92" s="105"/>
+      <c r="E92" s="105"/>
+      <c r="F92" s="105"/>
+      <c r="G92" s="105"/>
+      <c r="H92" s="105"/>
+      <c r="I92" s="105"/>
+      <c r="J92" s="105"/>
+      <c r="K92" s="106"/>
+    </row>
+    <row r="94" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="C94" s="90" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" ht="24" x14ac:dyDescent="0.2">
+      <c r="B96" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B97" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B98" s="92" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C99" s="96" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B100" s="93" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C101" s="91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C102" s="91" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C103" s="91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C104" s="91" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C105" s="91" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C106" s="91" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B107" s="93" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C108" s="91" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B109" s="111" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C110" s="96" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C111" s="96" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C112" s="96" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" ht="24" x14ac:dyDescent="0.2">
+      <c r="B114" s="13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B115" s="20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B116" s="90" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C117" s="96" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C118" s="96" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B119" s="87" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C120" s="91" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B121" s="92" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B122" s="92" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B123" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B124" s="112" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C125" s="94" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C126" s="91" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C127" s="94" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C128" s="91" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B129" s="87" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C130" s="91" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" ht="24" x14ac:dyDescent="0.2">
+      <c r="B132" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B133" s="87" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B134" s="90" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C135" s="96" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C136" s="96" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B137" s="90" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C138" s="91" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B139" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" ht="24" x14ac:dyDescent="0.2">
+      <c r="B141" s="13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B142" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B143" s="113" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5260,11 +9407,33 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5314,10 +9483,10 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
@@ -5685,243 +9854,243 @@
   <sheetData>
     <row r="2" spans="14:21" x14ac:dyDescent="0.2">
       <c r="N2" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q2" t="s">
         <v>169</v>
       </c>
-      <c r="Q2" t="s">
-        <v>170</v>
-      </c>
     </row>
     <row r="3" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O3" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="44"/>
+      <c r="O3" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="53"/>
     </row>
     <row r="4" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O4" s="45"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="47"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="56"/>
     </row>
     <row r="5" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O5" s="45"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="47"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O6" s="45"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="47"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="55"/>
+      <c r="U6" s="56"/>
     </row>
     <row r="7" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O7" s="45"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="47"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="56"/>
     </row>
     <row r="8" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O8" s="45"/>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="47"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="55"/>
+      <c r="U8" s="56"/>
     </row>
     <row r="9" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O9" s="45"/>
-      <c r="P9" s="77"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="77"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="47"/>
+      <c r="O9" s="57"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
+      <c r="U9" s="56"/>
     </row>
     <row r="10" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O10" s="48"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="50"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="59"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="59"/>
+      <c r="U10" s="60"/>
     </row>
     <row r="11" spans="14:21" x14ac:dyDescent="0.2">
       <c r="N11" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O12" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="44"/>
+      <c r="O12" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="53"/>
     </row>
     <row r="13" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O13" s="45"/>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="47"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="56"/>
     </row>
     <row r="14" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O14" s="45"/>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="47"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="55"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="55"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="56"/>
     </row>
     <row r="15" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O15" s="45"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="47"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="55"/>
+      <c r="U15" s="56"/>
     </row>
     <row r="16" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O16" s="45"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="77"/>
-      <c r="U16" s="47"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="55"/>
+      <c r="U16" s="56"/>
     </row>
     <row r="17" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O17" s="45"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="47"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="56"/>
     </row>
     <row r="18" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O18" s="45"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="77"/>
-      <c r="S18" s="77"/>
-      <c r="T18" s="77"/>
-      <c r="U18" s="47"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="55"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="55"/>
+      <c r="U18" s="56"/>
     </row>
     <row r="19" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O19" s="48"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="50"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="59"/>
+      <c r="R19" s="59"/>
+      <c r="S19" s="59"/>
+      <c r="T19" s="59"/>
+      <c r="U19" s="60"/>
     </row>
     <row r="20" spans="14:21" x14ac:dyDescent="0.2">
       <c r="N20" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O21" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="44"/>
+      <c r="O21" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="52"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="52"/>
+      <c r="U21" s="53"/>
     </row>
     <row r="22" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O22" s="45"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="77"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
-      <c r="U22" s="47"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="55"/>
+      <c r="Q22" s="55"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="56"/>
     </row>
     <row r="23" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O23" s="45"/>
-      <c r="P23" s="77"/>
-      <c r="Q23" s="77"/>
-      <c r="R23" s="77"/>
-      <c r="S23" s="77"/>
-      <c r="T23" s="77"/>
-      <c r="U23" s="47"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="55"/>
+      <c r="R23" s="55"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="55"/>
+      <c r="U23" s="56"/>
     </row>
     <row r="24" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O24" s="45"/>
-      <c r="P24" s="77"/>
-      <c r="Q24" s="77"/>
-      <c r="R24" s="77"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
-      <c r="U24" s="47"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="55"/>
+      <c r="U24" s="56"/>
     </row>
     <row r="25" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O25" s="45"/>
-      <c r="P25" s="77"/>
-      <c r="Q25" s="77"/>
-      <c r="R25" s="77"/>
-      <c r="S25" s="77"/>
-      <c r="T25" s="77"/>
-      <c r="U25" s="47"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="56"/>
     </row>
     <row r="26" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O26" s="45"/>
-      <c r="P26" s="77"/>
-      <c r="Q26" s="77"/>
-      <c r="R26" s="77"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="77"/>
-      <c r="U26" s="47"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="55"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="56"/>
     </row>
     <row r="27" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O27" s="45"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-      <c r="R27" s="77"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="77"/>
-      <c r="U27" s="47"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="56"/>
     </row>
     <row r="28" spans="14:21" x14ac:dyDescent="0.2">
-      <c r="O28" s="48"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="50"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
